--- a/school_2/1) walls/walls_sh2.xlsx
+++ b/school_2/1) walls/walls_sh2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="КП" sheetId="3" r:id="rId1"/>
@@ -21,13 +21,15 @@
     <sheet name="3.1-Ок-Ш2_НЗ" sheetId="7" r:id="rId7"/>
     <sheet name="3.2-Ок-Ш2" sheetId="5" r:id="rId8"/>
     <sheet name="4.1-Ст" sheetId="6" r:id="rId9"/>
+    <sheet name="6.1ГКЛ" sheetId="12" r:id="rId10"/>
+    <sheet name="Лист2" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2833" uniqueCount="1071">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -11532,6 +11534,27 @@
   </si>
   <si>
     <t>5.1-Пликта</t>
+  </si>
+  <si>
+    <t>ЗШ-1</t>
+  </si>
+  <si>
+    <t>ЗШ-3</t>
+  </si>
+  <si>
+    <t>ЗШ-4</t>
+  </si>
+  <si>
+    <t>ЗШ-2</t>
+  </si>
+  <si>
+    <t>ПО-4</t>
+  </si>
+  <si>
+    <t>12,3</t>
+  </si>
+  <si>
+    <t>помещения</t>
   </si>
 </sst>
 </file>
@@ -11744,7 +11767,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11779,6 +11802,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -12015,7 +12044,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -12305,6 +12334,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -13769,43 +13809,43 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="112" t="s">
+      <c r="A4" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
     </row>
     <row r="5" spans="1:11" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
@@ -25026,15 +25066,15 @@
       <c r="B501" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="C501" s="107" t="s">
+      <c r="C501" s="112" t="s">
         <v>778</v>
       </c>
-      <c r="D501" s="108"/>
-      <c r="E501" s="108"/>
-      <c r="F501" s="108"/>
-      <c r="G501" s="108"/>
-      <c r="H501" s="108"/>
-      <c r="I501" s="109"/>
+      <c r="D501" s="113"/>
+      <c r="E501" s="113"/>
+      <c r="F501" s="113"/>
+      <c r="G501" s="113"/>
+      <c r="H501" s="113"/>
+      <c r="I501" s="114"/>
     </row>
     <row r="502" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
@@ -25070,15 +25110,15 @@
       <c r="B503" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C503" s="107" t="s">
+      <c r="C503" s="112" t="s">
         <v>787</v>
       </c>
-      <c r="D503" s="108"/>
-      <c r="E503" s="108"/>
-      <c r="F503" s="108"/>
-      <c r="G503" s="108"/>
-      <c r="H503" s="108"/>
-      <c r="I503" s="109"/>
+      <c r="D503" s="113"/>
+      <c r="E503" s="113"/>
+      <c r="F503" s="113"/>
+      <c r="G503" s="113"/>
+      <c r="H503" s="113"/>
+      <c r="I503" s="114"/>
     </row>
     <row r="504" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
@@ -25087,15 +25127,15 @@
       <c r="B504" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="C504" s="107" t="s">
+      <c r="C504" s="112" t="s">
         <v>790</v>
       </c>
-      <c r="D504" s="108"/>
-      <c r="E504" s="108"/>
-      <c r="F504" s="108"/>
-      <c r="G504" s="108"/>
-      <c r="H504" s="108"/>
-      <c r="I504" s="109"/>
+      <c r="D504" s="113"/>
+      <c r="E504" s="113"/>
+      <c r="F504" s="113"/>
+      <c r="G504" s="113"/>
+      <c r="H504" s="113"/>
+      <c r="I504" s="114"/>
     </row>
     <row r="505" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
@@ -25131,15 +25171,15 @@
       <c r="B506" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="C506" s="107" t="s">
+      <c r="C506" s="112" t="s">
         <v>798</v>
       </c>
-      <c r="D506" s="108"/>
-      <c r="E506" s="108"/>
-      <c r="F506" s="108"/>
-      <c r="G506" s="108"/>
-      <c r="H506" s="108"/>
-      <c r="I506" s="109"/>
+      <c r="D506" s="113"/>
+      <c r="E506" s="113"/>
+      <c r="F506" s="113"/>
+      <c r="G506" s="113"/>
+      <c r="H506" s="113"/>
+      <c r="I506" s="114"/>
     </row>
     <row r="507" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
@@ -25148,15 +25188,15 @@
       <c r="B507" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="C507" s="107" t="s">
+      <c r="C507" s="112" t="s">
         <v>801</v>
       </c>
-      <c r="D507" s="108"/>
-      <c r="E507" s="108"/>
-      <c r="F507" s="108"/>
-      <c r="G507" s="108"/>
-      <c r="H507" s="108"/>
-      <c r="I507" s="109"/>
+      <c r="D507" s="113"/>
+      <c r="E507" s="113"/>
+      <c r="F507" s="113"/>
+      <c r="G507" s="113"/>
+      <c r="H507" s="113"/>
+      <c r="I507" s="114"/>
     </row>
     <row r="508" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
@@ -25165,15 +25205,15 @@
       <c r="B508" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="C508" s="107" t="s">
+      <c r="C508" s="112" t="s">
         <v>778</v>
       </c>
-      <c r="D508" s="108"/>
-      <c r="E508" s="108"/>
-      <c r="F508" s="108"/>
-      <c r="G508" s="108"/>
-      <c r="H508" s="108"/>
-      <c r="I508" s="109"/>
+      <c r="D508" s="113"/>
+      <c r="E508" s="113"/>
+      <c r="F508" s="113"/>
+      <c r="G508" s="113"/>
+      <c r="H508" s="113"/>
+      <c r="I508" s="114"/>
     </row>
     <row r="509" spans="1:9" ht="90" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
@@ -25242,6 +25282,804 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="128" t="s">
+        <v>829</v>
+      </c>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+    </row>
+    <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
+        <v>830</v>
+      </c>
+      <c r="B2" s="129" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="132" t="s">
+        <v>814</v>
+      </c>
+      <c r="I2" s="133"/>
+      <c r="J2" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="107">
+        <v>1</v>
+      </c>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="137" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="138"/>
+      <c r="J3" s="107" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="40"/>
+    </row>
+    <row r="4" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="107">
+        <v>2</v>
+      </c>
+      <c r="B4" s="134">
+        <v>2</v>
+      </c>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="138"/>
+      <c r="J4" s="107" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="40"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="127"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+    </row>
+    <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="41" t="s">
+        <v>832</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>833</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>834</v>
+      </c>
+      <c r="D6" s="46"/>
+      <c r="E6" s="41" t="s">
+        <v>832</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>833</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>834</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+    </row>
+    <row r="8" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+    </row>
+    <row r="9" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+    </row>
+    <row r="10" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+    </row>
+    <row r="11" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="46"/>
+      <c r="F11" s="44" t="s">
+        <v>844</v>
+      </c>
+      <c r="G11">
+        <f>SUM(G7:G10)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+    </row>
+    <row r="12" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+    </row>
+    <row r="13" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+    </row>
+    <row r="15" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+    </row>
+    <row r="16" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+    </row>
+    <row r="17" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="42"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+    </row>
+    <row r="19" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+    </row>
+    <row r="20" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+    </row>
+    <row r="21" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+    </row>
+    <row r="22" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="42"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+    </row>
+    <row r="23" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+    </row>
+    <row r="26" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="42"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+    </row>
+    <row r="27" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="42"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+    </row>
+    <row r="29" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="42"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+    </row>
+    <row r="31" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+    </row>
+    <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="42"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="43"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+    </row>
+    <row r="34" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+    </row>
+    <row r="35" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+    </row>
+    <row r="36" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="42"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+    </row>
+    <row r="37" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+    </row>
+    <row r="38" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
+    </row>
+    <row r="39" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+    </row>
+    <row r="40" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="46"/>
+      <c r="K40" s="46"/>
+    </row>
+    <row r="41" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+    </row>
+    <row r="42" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="44" t="s">
+        <v>844</v>
+      </c>
+      <c r="C42">
+        <f>SUM(C7:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C6:I31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="11.6640625" style="109" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="108" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D6" s="108">
+        <v>186.9</v>
+      </c>
+      <c r="E6" s="108">
+        <v>35.4</v>
+      </c>
+      <c r="G6" s="108" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H6">
+        <v>187.4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="108" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D7" s="108">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="108">
+        <v>10.8</v>
+      </c>
+      <c r="G7" s="108" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H7">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="108" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D8" s="108">
+        <v>13.8</v>
+      </c>
+      <c r="E8" s="108">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D10">
+        <v>60.3</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H10">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D12">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="E12">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H12">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="I12">
+        <v>71.900000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F21" s="109" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="24" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F24" s="109" t="s">
+        <v>976</v>
+      </c>
+      <c r="G24">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="25" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F25" s="109" t="s">
+        <v>990</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F26" s="109" t="s">
+        <v>982</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F27" s="109" t="s">
+        <v>998</v>
+      </c>
+      <c r="H27">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="28" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F28" s="109" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H28">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F29" s="109" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F30" s="109" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G30" s="110" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="31" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F31" s="109" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G31" s="111">
+        <v>5.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -30147,29 +30985,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
     </row>
     <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
       <c r="G2" s="79" t="s">
         <v>814</v>
       </c>
@@ -30184,13 +31022,13 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
       <c r="G3" s="90" t="s">
         <v>531</v>
       </c>
@@ -30202,17 +31040,17 @@
         <v>208.6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
       <c r="G4" s="88" t="s">
         <v>539</v>
       </c>
@@ -30224,17 +31062,17 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="79">
         <v>3</v>
       </c>
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
       <c r="G5" s="90" t="s">
         <v>546</v>
       </c>
@@ -30250,13 +31088,13 @@
       <c r="A6" s="79">
         <v>4</v>
       </c>
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
       <c r="G6" s="88" t="s">
         <v>553</v>
       </c>
@@ -30272,13 +31110,13 @@
       <c r="A7" s="79">
         <v>5</v>
       </c>
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
       <c r="G7" s="90" t="s">
         <v>560</v>
       </c>
@@ -30291,15 +31129,15 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="115"/>
-      <c r="B8" s="115"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -30314,7 +31152,7 @@
       <c r="D9" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="E9" s="114"/>
+      <c r="E9" s="119"/>
       <c r="F9" s="79" t="s">
         <v>1055</v>
       </c>
@@ -30341,7 +31179,7 @@
       <c r="D10" s="82">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E10" s="114"/>
+      <c r="E10" s="119"/>
       <c r="F10" s="93">
         <v>3</v>
       </c>
@@ -30368,7 +31206,7 @@
       <c r="D11" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E11" s="114"/>
+      <c r="E11" s="119"/>
       <c r="F11" s="93">
         <v>3</v>
       </c>
@@ -30395,7 +31233,7 @@
       <c r="D12" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E12" s="114"/>
+      <c r="E12" s="119"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -30422,7 +31260,7 @@
       <c r="D13" s="82">
         <v>31.6</v>
       </c>
-      <c r="E13" s="114"/>
+      <c r="E13" s="119"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -30449,7 +31287,7 @@
       <c r="D14" s="95">
         <v>5.9</v>
       </c>
-      <c r="E14" s="114"/>
+      <c r="E14" s="119"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -30476,7 +31314,7 @@
       <c r="D15" s="95">
         <v>36.9</v>
       </c>
-      <c r="E15" s="114"/>
+      <c r="E15" s="119"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -30503,7 +31341,7 @@
       <c r="D16" s="95">
         <v>33.9</v>
       </c>
-      <c r="E16" s="114"/>
+      <c r="E16" s="119"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -30530,7 +31368,7 @@
       <c r="D17" s="82">
         <v>5.7</v>
       </c>
-      <c r="E17" s="114"/>
+      <c r="E17" s="119"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -30557,7 +31395,7 @@
       <c r="D18" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E18" s="114"/>
+      <c r="E18" s="119"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -30584,7 +31422,7 @@
       <c r="D19" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E19" s="114"/>
+      <c r="E19" s="119"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -30611,7 +31449,7 @@
       <c r="D20" s="82">
         <v>44.2</v>
       </c>
-      <c r="E20" s="114"/>
+      <c r="E20" s="119"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -30663,30 +31501,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
     </row>
     <row r="2" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
       <c r="G2" s="79" t="s">
         <v>814</v>
       </c>
@@ -30702,13 +31540,13 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="121" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
       <c r="G3" s="88" t="s">
         <v>418</v>
       </c>
@@ -30727,13 +31565,13 @@
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
       <c r="G4" s="100" t="s">
         <v>531</v>
       </c>
@@ -30746,17 +31584,17 @@
       </c>
       <c r="J4" s="100"/>
     </row>
-    <row r="5" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="79">
         <v>3</v>
       </c>
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
       <c r="G5" s="88" t="s">
         <v>539</v>
       </c>
@@ -30769,17 +31607,17 @@
       </c>
       <c r="J5" s="100"/>
     </row>
-    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="79">
         <v>4</v>
       </c>
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
       <c r="G6" s="100" t="s">
         <v>546</v>
       </c>
@@ -30796,13 +31634,13 @@
       <c r="A7" s="79">
         <v>5</v>
       </c>
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
       <c r="G7" s="88" t="s">
         <v>553</v>
       </c>
@@ -30819,13 +31657,13 @@
       <c r="A8" s="79">
         <v>6</v>
       </c>
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="121" t="s">
         <v>424</v>
       </c>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
       <c r="G8" s="100" t="s">
         <v>560</v>
       </c>
@@ -30842,12 +31680,12 @@
       <c r="A9" s="79">
         <v>7</v>
       </c>
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="122" t="s">
         <v>1061</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="119"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
       <c r="F9" s="79" t="s">
         <v>1059</v>
       </c>
@@ -30866,16 +31704,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="115"/>
-      <c r="B10" s="115"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -30890,7 +31728,7 @@
       <c r="D11" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="E11" s="114"/>
+      <c r="E11" s="119"/>
       <c r="F11" s="79" t="s">
         <v>1055</v>
       </c>
@@ -30903,7 +31741,7 @@
       <c r="I11" s="79" t="s">
         <v>831</v>
       </c>
-      <c r="J11" s="121"/>
+      <c r="J11" s="126"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="92">
@@ -30918,7 +31756,7 @@
       <c r="D12" s="95">
         <v>11.7</v>
       </c>
-      <c r="E12" s="114"/>
+      <c r="E12" s="119"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -30931,7 +31769,7 @@
       <c r="I12" s="93">
         <v>33</v>
       </c>
-      <c r="J12" s="121"/>
+      <c r="J12" s="126"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="102">
@@ -30946,7 +31784,7 @@
       <c r="D13" s="101">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E13" s="114"/>
+      <c r="E13" s="119"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -30959,7 +31797,7 @@
       <c r="I13" s="93">
         <v>14.1</v>
       </c>
-      <c r="J13" s="121"/>
+      <c r="J13" s="126"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="92">
@@ -30974,7 +31812,7 @@
       <c r="D14" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E14" s="114"/>
+      <c r="E14" s="119"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -30987,7 +31825,7 @@
       <c r="I14" s="93">
         <v>8.1</v>
       </c>
-      <c r="J14" s="121"/>
+      <c r="J14" s="126"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="102">
@@ -31002,7 +31840,7 @@
       <c r="D15" s="101">
         <v>2.6</v>
       </c>
-      <c r="E15" s="114"/>
+      <c r="E15" s="119"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -31015,7 +31853,7 @@
       <c r="I15" s="93">
         <v>65.8</v>
       </c>
-      <c r="J15" s="121"/>
+      <c r="J15" s="126"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="92">
@@ -31030,7 +31868,7 @@
       <c r="D16" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E16" s="114"/>
+      <c r="E16" s="119"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -31043,7 +31881,7 @@
       <c r="I16" s="93">
         <v>2.6</v>
       </c>
-      <c r="J16" s="121"/>
+      <c r="J16" s="126"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="92">
@@ -31058,7 +31896,7 @@
       <c r="D17" s="95">
         <v>11.7</v>
       </c>
-      <c r="E17" s="114"/>
+      <c r="E17" s="119"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -31071,7 +31909,7 @@
       <c r="I17" s="93">
         <v>13.6</v>
       </c>
-      <c r="J17" s="121"/>
+      <c r="J17" s="126"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="102">
@@ -31086,7 +31924,7 @@
       <c r="D18" s="101">
         <v>31.6</v>
       </c>
-      <c r="E18" s="114"/>
+      <c r="E18" s="119"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -31099,7 +31937,7 @@
       <c r="I18" s="93">
         <v>5.8</v>
       </c>
-      <c r="J18" s="121"/>
+      <c r="J18" s="126"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="92">
@@ -31114,7 +31952,7 @@
       <c r="D19" s="95">
         <v>5.9</v>
       </c>
-      <c r="E19" s="114"/>
+      <c r="E19" s="119"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -31127,7 +31965,7 @@
       <c r="I19" s="93">
         <v>67.8</v>
       </c>
-      <c r="J19" s="121"/>
+      <c r="J19" s="126"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="92">
@@ -31142,7 +31980,7 @@
       <c r="D20" s="95">
         <v>36.9</v>
       </c>
-      <c r="E20" s="114"/>
+      <c r="E20" s="119"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -31155,7 +31993,7 @@
       <c r="I20" s="93">
         <v>1.8</v>
       </c>
-      <c r="J20" s="121"/>
+      <c r="J20" s="126"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="92">
@@ -31170,7 +32008,7 @@
       <c r="D21" s="95">
         <v>33.9</v>
       </c>
-      <c r="E21" s="114"/>
+      <c r="E21" s="119"/>
       <c r="F21" s="93">
         <v>3</v>
       </c>
@@ -31183,7 +32021,7 @@
       <c r="I21" s="93">
         <v>35.4</v>
       </c>
-      <c r="J21" s="121"/>
+      <c r="J21" s="126"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="92">
@@ -31198,7 +32036,7 @@
       <c r="D22" s="95">
         <v>11.9</v>
       </c>
-      <c r="E22" s="114"/>
+      <c r="E22" s="119"/>
       <c r="F22" s="93">
         <v>3</v>
       </c>
@@ -31211,7 +32049,7 @@
       <c r="I22" s="93">
         <v>5.9</v>
       </c>
-      <c r="J22" s="121"/>
+      <c r="J22" s="126"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="102">
@@ -31226,7 +32064,7 @@
       <c r="D23" s="101">
         <v>5.7</v>
       </c>
-      <c r="E23" s="114"/>
+      <c r="E23" s="119"/>
       <c r="F23" s="93">
         <v>3</v>
       </c>
@@ -31239,7 +32077,7 @@
       <c r="I23" s="93">
         <v>29.5</v>
       </c>
-      <c r="J23" s="121"/>
+      <c r="J23" s="126"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="92">
@@ -31254,7 +32092,7 @@
       <c r="D24" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E24" s="114"/>
+      <c r="E24" s="119"/>
       <c r="F24" s="93">
         <v>3</v>
       </c>
@@ -31267,7 +32105,7 @@
       <c r="I24" s="93">
         <v>36.9</v>
       </c>
-      <c r="J24" s="121"/>
+      <c r="J24" s="126"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="102">
@@ -31282,7 +32120,7 @@
       <c r="D25" s="101">
         <v>1.8</v>
       </c>
-      <c r="E25" s="114"/>
+      <c r="E25" s="119"/>
       <c r="F25" s="93">
         <v>3</v>
       </c>
@@ -31295,7 +32133,7 @@
       <c r="I25" s="93">
         <v>36.5</v>
       </c>
-      <c r="J25" s="121"/>
+      <c r="J25" s="126"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="92">
@@ -31310,7 +32148,7 @@
       <c r="D26" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E26" s="114"/>
+      <c r="E26" s="119"/>
       <c r="F26" s="96">
         <v>3</v>
       </c>
@@ -31323,7 +32161,7 @@
       <c r="I26" s="96">
         <v>29.5</v>
       </c>
-      <c r="J26" s="121"/>
+      <c r="J26" s="126"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="102">
@@ -31338,7 +32176,7 @@
       <c r="D27" s="101">
         <v>44.2</v>
       </c>
-      <c r="E27" s="114"/>
+      <c r="E27" s="119"/>
       <c r="F27" s="98">
         <v>3</v>
       </c>
@@ -31352,7 +32190,7 @@
         <f>1.08*13.5</f>
         <v>14.580000000000002</v>
       </c>
-      <c r="J27" s="121"/>
+      <c r="J27" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -31911,17 +32749,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="128" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -31929,18 +32767,18 @@
       <c r="A2" s="36" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="127" t="s">
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="132" t="s">
         <v>814</v>
       </c>
-      <c r="I2" s="128"/>
+      <c r="I2" s="133"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -31952,33 +32790,33 @@
       <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="132" t="s">
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="133"/>
+      <c r="I3" s="138"/>
       <c r="J3" s="39" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="40"/>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="122"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="127"/>
+      <c r="K4" s="127"/>
     </row>
     <row r="5" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="41" t="s">

--- a/school_2/1) walls/walls_sh2.xlsx
+++ b/school_2/1) walls/walls_sh2.xlsx
@@ -9,38 +9,39 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520"/>
   </bookViews>
   <sheets>
-    <sheet name="8.4отк.лк" sheetId="24" r:id="rId1"/>
-    <sheet name="8.3шп.лк" sheetId="23" r:id="rId2"/>
-    <sheet name="8.2умнь.дв" sheetId="22" r:id="rId3"/>
-    <sheet name="8.1дврн.откс" sheetId="21" r:id="rId4"/>
-    <sheet name="7.8фрхв" sheetId="20" r:id="rId5"/>
-    <sheet name="7.7внеш.блк" sheetId="19" r:id="rId6"/>
-    <sheet name="7.6прмч" sheetId="18" r:id="rId7"/>
-    <sheet name="КП" sheetId="3" r:id="rId8"/>
-    <sheet name="Плитки" sheetId="8" r:id="rId9"/>
-    <sheet name="Пом" sheetId="9" r:id="rId10"/>
-    <sheet name="7.4Блок" sheetId="17" r:id="rId11"/>
-    <sheet name="7.3Кирп1э" sheetId="16" r:id="rId12"/>
-    <sheet name="7.2КирпПодв" sheetId="15" r:id="rId13"/>
-    <sheet name="7.1ПГП" sheetId="14" r:id="rId14"/>
-    <sheet name="6.1ГКЛ" sheetId="12" r:id="rId15"/>
-    <sheet name="5.2_остаток" sheetId="11" r:id="rId16"/>
-    <sheet name="5.1_плтк" sheetId="10" r:id="rId17"/>
-    <sheet name="3.2-Ок-Ш2" sheetId="5" r:id="rId18"/>
-    <sheet name="4.1-Ст" sheetId="6" r:id="rId19"/>
-    <sheet name="3.1-Ок-Ш2_НЗ" sheetId="7" r:id="rId20"/>
-    <sheet name="3.1-Ок-Ш2" sheetId="4" r:id="rId21"/>
-    <sheet name="Лист2" sheetId="13" r:id="rId22"/>
+    <sheet name="8.5дфрг" sheetId="25" r:id="rId1"/>
+    <sheet name="8.4отк.лк" sheetId="24" r:id="rId2"/>
+    <sheet name="8.3шп.лк" sheetId="23" r:id="rId3"/>
+    <sheet name="8.2умнь.дв" sheetId="22" r:id="rId4"/>
+    <sheet name="8.1дврн.откс" sheetId="21" r:id="rId5"/>
+    <sheet name="7.8фрхв" sheetId="20" r:id="rId6"/>
+    <sheet name="7.7внеш.блк" sheetId="19" r:id="rId7"/>
+    <sheet name="7.6прмч" sheetId="18" r:id="rId8"/>
+    <sheet name="КП" sheetId="3" r:id="rId9"/>
+    <sheet name="Плитки" sheetId="8" r:id="rId10"/>
+    <sheet name="Пом" sheetId="9" r:id="rId11"/>
+    <sheet name="7.4Блок" sheetId="17" r:id="rId12"/>
+    <sheet name="7.3Кирп1э" sheetId="16" r:id="rId13"/>
+    <sheet name="7.2КирпПодв" sheetId="15" r:id="rId14"/>
+    <sheet name="7.1ПГП" sheetId="14" r:id="rId15"/>
+    <sheet name="6.1ГКЛ" sheetId="12" r:id="rId16"/>
+    <sheet name="5.2_остаток" sheetId="11" r:id="rId17"/>
+    <sheet name="5.1_плтк" sheetId="10" r:id="rId18"/>
+    <sheet name="3.2-Ок-Ш2" sheetId="5" r:id="rId19"/>
+    <sheet name="4.1-Ст" sheetId="6" r:id="rId20"/>
+    <sheet name="3.1-Ок-Ш2_НЗ" sheetId="7" r:id="rId21"/>
+    <sheet name="3.1-Ок-Ш2" sheetId="4" r:id="rId22"/>
+    <sheet name="Лист2" sheetId="13" r:id="rId23"/>
   </sheets>
-  <calcPr calcId="152511" refMode="R1C1"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="1141">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -11789,6 +11790,15 @@
   </si>
   <si>
     <t>1-3 эт. Шпаклевка финишная лючков "Хаммер"</t>
+  </si>
+  <si>
+    <t>Объем, м3:</t>
+  </si>
+  <si>
+    <t>Пом.</t>
+  </si>
+  <si>
+    <t>Заделка мест прохождения воздуховодов</t>
   </si>
 </sst>
 </file>
@@ -12329,7 +12339,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -12768,6 +12778,15 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -12941,6 +12960,21 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -14284,235 +14318,993 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="158" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="112" customWidth="1"/>
-    <col min="3" max="3" width="17" style="112" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" style="112" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="112" customWidth="1"/>
-    <col min="6" max="6" width="26.6640625" style="112" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="112" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" style="112" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="112"/>
+    <col min="1" max="1" width="7.109375" style="165" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="112" customWidth="1"/>
+    <col min="3" max="3" width="2.21875" style="112" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="112" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="112" customWidth="1"/>
+    <col min="6" max="6" width="2" style="112" customWidth="1"/>
+    <col min="7" max="7" width="6" style="112" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="112" customWidth="1"/>
+    <col min="9" max="9" width="2.44140625" style="112" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="112" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="112" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="112"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-    </row>
-    <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="172"/>
+    </row>
+    <row r="2" spans="1:11" s="228" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="156" t="s">
-        <v>814</v>
-      </c>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="227"/>
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="K2" s="117" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="159" t="s">
-        <v>1133</v>
-      </c>
-      <c r="G3" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="160">
-        <f>E11</f>
-        <v>51.599999999999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="140">
-        <v>2</v>
-      </c>
-      <c r="B4" s="164" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="157" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G4" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="160">
-        <f>H3</f>
-        <v>51.599999999999994</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="140">
-        <v>3</v>
-      </c>
-      <c r="B5" s="164" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="157" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G5" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="160">
-        <f>H4</f>
-        <v>51.599999999999994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="173"/>
-      <c r="B6" s="173"/>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="173"/>
-      <c r="H6" s="173"/>
-    </row>
-    <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="226" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C3" s="226"/>
+      <c r="D3" s="226"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="226"/>
+      <c r="H3" s="226"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="115" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="229">
+        <f>K33+H34+E34+B35</f>
+        <v>8.0300000000000011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="176"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="114" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B5" s="114" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C5" s="170"/>
+      <c r="D5" s="114" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E5" s="114" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F5" s="225"/>
+      <c r="G5" s="114" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H5" s="164" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I5" s="171"/>
+      <c r="J5" s="114" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K5" s="114" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="114" t="s">
+        <v>835</v>
+      </c>
+      <c r="B6" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C6" s="170"/>
+      <c r="D6" s="114" t="s">
+        <v>856</v>
+      </c>
+      <c r="E6" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="F6" s="225"/>
+      <c r="G6" s="114" t="s">
+        <v>972</v>
+      </c>
+      <c r="H6" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I6" s="171"/>
+      <c r="J6" s="114" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K6" s="114">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="114" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B7" s="115" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C7" s="115" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D7" s="115" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E7" s="115" t="s">
-        <v>1128</v>
-      </c>
-      <c r="F7" s="167"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="114">
-        <v>1</v>
-      </c>
-      <c r="B8" s="139">
-        <v>20</v>
-      </c>
-      <c r="C8" s="161" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D8" s="162">
+        <v>837</v>
+      </c>
+      <c r="B7" s="114">
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="170"/>
+      <c r="D7" s="114" t="s">
+        <v>840</v>
+      </c>
+      <c r="E7" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="F7" s="225"/>
+      <c r="G7" s="114" t="s">
+        <v>973</v>
+      </c>
+      <c r="H7" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I7" s="171"/>
+      <c r="J7" s="114" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K7" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="114" t="s">
+        <v>839</v>
+      </c>
+      <c r="B8" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C8" s="170"/>
+      <c r="D8" s="114" t="s">
+        <v>857</v>
+      </c>
+      <c r="E8" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="F8" s="225"/>
+      <c r="G8" s="114" t="s">
+        <v>974</v>
+      </c>
+      <c r="H8" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I8" s="171"/>
+      <c r="J8" s="114" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K8" s="114">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="114" t="s">
+        <v>841</v>
+      </c>
+      <c r="B9" s="114">
+        <v>0.08</v>
+      </c>
+      <c r="C9" s="170"/>
+      <c r="D9" s="114" t="s">
+        <v>858</v>
+      </c>
+      <c r="E9" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="F9" s="225"/>
+      <c r="G9" s="114" t="s">
+        <v>975</v>
+      </c>
+      <c r="H9" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="I9" s="171"/>
+      <c r="J9" s="114" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K9" s="114">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="114" t="s">
+        <v>843</v>
+      </c>
+      <c r="B10" s="114">
+        <v>0.04</v>
+      </c>
+      <c r="C10" s="170"/>
+      <c r="D10" s="114" t="s">
+        <v>859</v>
+      </c>
+      <c r="E10" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="F10" s="225"/>
+      <c r="G10" s="114" t="s">
+        <v>976</v>
+      </c>
+      <c r="H10" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="171"/>
+      <c r="J10" s="114" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K10" s="114">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="114" t="s">
+        <v>945</v>
+      </c>
+      <c r="B11" s="114">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="170"/>
+      <c r="D11" s="114" t="s">
+        <v>860</v>
+      </c>
+      <c r="E11" s="114">
+        <v>0.18</v>
+      </c>
+      <c r="F11" s="225"/>
+      <c r="G11" s="114" t="s">
+        <v>978</v>
+      </c>
+      <c r="H11" s="114">
+        <v>0.05</v>
+      </c>
+      <c r="I11" s="171"/>
+      <c r="J11" s="114" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K11" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="114" t="s">
+        <v>946</v>
+      </c>
+      <c r="B12" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="C12" s="170"/>
+      <c r="D12" s="114" t="s">
+        <v>961</v>
+      </c>
+      <c r="E12" s="114">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="225"/>
+      <c r="G12" s="114" t="s">
+        <v>979</v>
+      </c>
+      <c r="H12" s="114">
+        <v>0.04</v>
+      </c>
+      <c r="I12" s="171"/>
+      <c r="J12" s="114" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K12" s="114">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="114" t="s">
+        <v>947</v>
+      </c>
+      <c r="B13" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="170"/>
+      <c r="D13" s="114" t="s">
+        <v>861</v>
+      </c>
+      <c r="E13" s="114">
+        <v>0.18</v>
+      </c>
+      <c r="F13" s="225"/>
+      <c r="G13" s="114" t="s">
+        <v>980</v>
+      </c>
+      <c r="H13" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="171"/>
+      <c r="J13" s="114" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K13" s="114">
         <v>0.2</v>
       </c>
-      <c r="E8" s="162">
-        <f>((0.7+(1.8*2))*0.2)*B8</f>
-        <v>17.2</v>
-      </c>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="168"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="114">
-        <v>2</v>
-      </c>
-      <c r="B9" s="139">
-        <v>18</v>
-      </c>
-      <c r="C9" s="161" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D9" s="162">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="114" t="s">
+        <v>845</v>
+      </c>
+      <c r="B14" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C14" s="170"/>
+      <c r="D14" s="114" t="s">
+        <v>862</v>
+      </c>
+      <c r="E14" s="114">
+        <v>0.17</v>
+      </c>
+      <c r="F14" s="225"/>
+      <c r="G14" s="114" t="s">
+        <v>981</v>
+      </c>
+      <c r="H14" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="I14" s="171"/>
+      <c r="J14" s="114" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K14" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="114" t="s">
+        <v>846</v>
+      </c>
+      <c r="B15" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C15" s="170"/>
+      <c r="D15" s="114" t="s">
+        <v>863</v>
+      </c>
+      <c r="E15" s="114">
+        <v>0.11</v>
+      </c>
+      <c r="F15" s="225"/>
+      <c r="G15" s="114" t="s">
+        <v>982</v>
+      </c>
+      <c r="H15" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="I15" s="171"/>
+      <c r="J15" s="114" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K15" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="114" t="s">
+        <v>847</v>
+      </c>
+      <c r="B16" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C16" s="170"/>
+      <c r="D16" s="114" t="s">
+        <v>864</v>
+      </c>
+      <c r="E16" s="114">
+        <v>0.15</v>
+      </c>
+      <c r="F16" s="225"/>
+      <c r="G16" s="114" t="s">
+        <v>983</v>
+      </c>
+      <c r="H16" s="114">
+        <v>0.22</v>
+      </c>
+      <c r="I16" s="171"/>
+      <c r="J16" s="114" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K16" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="114" t="s">
+        <v>848</v>
+      </c>
+      <c r="B17" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C17" s="170"/>
+      <c r="D17" s="114" t="s">
+        <v>865</v>
+      </c>
+      <c r="E17" s="114">
+        <v>0.11</v>
+      </c>
+      <c r="F17" s="225"/>
+      <c r="G17" s="114" t="s">
+        <v>984</v>
+      </c>
+      <c r="H17" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="I17" s="171"/>
+      <c r="J17" s="114" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K17" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="114" t="s">
+        <v>849</v>
+      </c>
+      <c r="B18" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C18" s="170"/>
+      <c r="D18" s="114" t="s">
+        <v>866</v>
+      </c>
+      <c r="E18" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="F18" s="225"/>
+      <c r="G18" s="114" t="s">
+        <v>985</v>
+      </c>
+      <c r="H18" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I18" s="171"/>
+      <c r="J18" s="114" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K18" s="114">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="114" t="s">
+        <v>850</v>
+      </c>
+      <c r="B19" s="114">
+        <v>0.13</v>
+      </c>
+      <c r="C19" s="170"/>
+      <c r="D19" s="114" t="s">
+        <v>963</v>
+      </c>
+      <c r="E19" s="114">
+        <v>0.03</v>
+      </c>
+      <c r="F19" s="225"/>
+      <c r="G19" s="114" t="s">
+        <v>986</v>
+      </c>
+      <c r="H19" s="114">
+        <v>0.03</v>
+      </c>
+      <c r="I19" s="171"/>
+      <c r="J19" s="114" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K19" s="114">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="114" t="s">
+        <v>948</v>
+      </c>
+      <c r="B20" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="C20" s="170"/>
+      <c r="D20" s="114" t="s">
+        <v>964</v>
+      </c>
+      <c r="E20" s="114">
+        <v>0.04</v>
+      </c>
+      <c r="F20" s="225"/>
+      <c r="G20" s="114" t="s">
+        <v>988</v>
+      </c>
+      <c r="H20" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="171"/>
+      <c r="J20" s="114" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K20" s="114">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="114" t="s">
+        <v>950</v>
+      </c>
+      <c r="B21" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="C21" s="170"/>
+      <c r="D21" s="114" t="s">
+        <v>965</v>
+      </c>
+      <c r="E21" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="F21" s="225"/>
+      <c r="G21" s="114" t="s">
+        <v>989</v>
+      </c>
+      <c r="H21" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="I21" s="171"/>
+      <c r="J21" s="114" t="s">
+        <v>1021</v>
+      </c>
+      <c r="K21" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="114" t="s">
+        <v>951</v>
+      </c>
+      <c r="B22" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="C22" s="170"/>
+      <c r="D22" s="114" t="s">
+        <v>966</v>
+      </c>
+      <c r="E22" s="114">
+        <v>0.03</v>
+      </c>
+      <c r="F22" s="225"/>
+      <c r="G22" s="114" t="s">
+        <v>990</v>
+      </c>
+      <c r="H22" s="114">
         <v>0.2</v>
       </c>
-      <c r="E9" s="162">
-        <f t="shared" ref="E9:E10" si="0">((0.7+(1.8*2))*0.2)*B9</f>
-        <v>15.48</v>
-      </c>
-      <c r="F9" s="167"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="168"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="114">
-        <v>3</v>
-      </c>
-      <c r="B10" s="139">
-        <v>22</v>
-      </c>
-      <c r="C10" s="161" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D10" s="162">
+      <c r="I22" s="171"/>
+      <c r="J22" s="114" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K22" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="114" t="s">
+        <v>851</v>
+      </c>
+      <c r="B23" s="114">
+        <v>0.17</v>
+      </c>
+      <c r="C23" s="170"/>
+      <c r="D23" s="114" t="s">
+        <v>967</v>
+      </c>
+      <c r="E23" s="114">
+        <v>0.06</v>
+      </c>
+      <c r="F23" s="225"/>
+      <c r="G23" s="114" t="s">
+        <v>992</v>
+      </c>
+      <c r="H23" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="I23" s="171"/>
+      <c r="J23" s="114" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K23" s="114">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="114" t="s">
+        <v>852</v>
+      </c>
+      <c r="B24" s="114">
+        <v>0.08</v>
+      </c>
+      <c r="C24" s="170"/>
+      <c r="D24" s="114" t="s">
+        <v>867</v>
+      </c>
+      <c r="E24" s="114">
+        <v>0.11</v>
+      </c>
+      <c r="F24" s="225"/>
+      <c r="G24" s="114" t="s">
+        <v>993</v>
+      </c>
+      <c r="H24" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I24" s="171"/>
+      <c r="J24" s="114" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K24" s="114">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="114" t="s">
+        <v>954</v>
+      </c>
+      <c r="B25" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="C25" s="170"/>
+      <c r="D25" s="114" t="s">
+        <v>868</v>
+      </c>
+      <c r="E25" s="114">
+        <v>0.21</v>
+      </c>
+      <c r="F25" s="225"/>
+      <c r="G25" s="114" t="s">
+        <v>994</v>
+      </c>
+      <c r="H25" s="114">
+        <v>0.16</v>
+      </c>
+      <c r="I25" s="171"/>
+      <c r="J25" s="114" t="s">
+        <v>1026</v>
+      </c>
+      <c r="K25" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="114" t="s">
+        <v>955</v>
+      </c>
+      <c r="B26" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="C26" s="170"/>
+      <c r="D26" s="114" t="s">
+        <v>869</v>
+      </c>
+      <c r="E26" s="114">
+        <v>0.18</v>
+      </c>
+      <c r="F26" s="225"/>
+      <c r="G26" s="114" t="s">
+        <v>996</v>
+      </c>
+      <c r="H26" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="I26" s="171"/>
+      <c r="J26" s="114" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K26" s="114">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="114" t="s">
+        <v>956</v>
+      </c>
+      <c r="B27" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="C27" s="170"/>
+      <c r="D27" s="114" t="s">
+        <v>870</v>
+      </c>
+      <c r="E27" s="114">
+        <v>0.02</v>
+      </c>
+      <c r="F27" s="225"/>
+      <c r="G27" s="114" t="s">
+        <v>997</v>
+      </c>
+      <c r="H27" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="I27" s="171"/>
+      <c r="J27" s="114" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K27" s="114">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="114" t="s">
+        <v>957</v>
+      </c>
+      <c r="B28" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="C28" s="170"/>
+      <c r="D28" s="114" t="s">
+        <v>971</v>
+      </c>
+      <c r="E28" s="114">
+        <v>0.03</v>
+      </c>
+      <c r="F28" s="225"/>
+      <c r="G28" s="114" t="s">
+        <v>998</v>
+      </c>
+      <c r="H28" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="I28" s="171"/>
+      <c r="J28" s="114" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K28" s="114">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="114" t="s">
+        <v>853</v>
+      </c>
+      <c r="B29" s="114">
+        <v>0.08</v>
+      </c>
+      <c r="C29" s="170"/>
+      <c r="D29" s="114" t="s">
+        <v>871</v>
+      </c>
+      <c r="E29" s="114">
+        <v>0.18</v>
+      </c>
+      <c r="F29" s="225"/>
+      <c r="G29" s="114" t="s">
+        <v>999</v>
+      </c>
+      <c r="H29" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I29" s="171"/>
+      <c r="J29" s="114" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K29" s="114">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="114" t="s">
+        <v>854</v>
+      </c>
+      <c r="B30" s="114">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="170"/>
+      <c r="D30" s="114" t="s">
+        <v>872</v>
+      </c>
+      <c r="E30" s="114">
         <v>0.2</v>
       </c>
-      <c r="E10" s="162">
-        <f t="shared" si="0"/>
-        <v>18.919999999999998</v>
-      </c>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="114"/>
-      <c r="B11" s="139">
-        <f>SUM(B8:B10)</f>
-        <v>60</v>
-      </c>
-      <c r="C11" s="163"/>
-      <c r="D11" s="163" t="s">
+      <c r="F30" s="225"/>
+      <c r="G30" s="114" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="I30" s="171"/>
+      <c r="J30" s="114" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K30" s="114">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="114" t="s">
+        <v>855</v>
+      </c>
+      <c r="B31" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C31" s="170"/>
+      <c r="D31" s="114" t="s">
+        <v>873</v>
+      </c>
+      <c r="E31" s="114">
+        <v>0.17</v>
+      </c>
+      <c r="F31" s="225"/>
+      <c r="G31" s="114" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H31" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I31" s="171"/>
+      <c r="J31" s="114" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K31" s="114">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="114" t="s">
+        <v>958</v>
+      </c>
+      <c r="B32" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="C32" s="170"/>
+      <c r="D32" s="114" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E32" s="114">
+        <v>0.05</v>
+      </c>
+      <c r="F32" s="225"/>
+      <c r="G32" s="114" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H32" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I32" s="171"/>
+      <c r="J32" s="114" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K32" s="114">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="114" t="s">
+        <v>959</v>
+      </c>
+      <c r="B33" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="C33" s="170"/>
+      <c r="D33" s="114" t="s">
+        <v>874</v>
+      </c>
+      <c r="E33" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="F33" s="225"/>
+      <c r="G33" s="114" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H33" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I33" s="171"/>
+      <c r="J33" s="166" t="s">
         <v>844</v>
       </c>
-      <c r="E11" s="162">
-        <f>SUM(E8:E10)</f>
-        <v>51.599999999999994</v>
-      </c>
-      <c r="F11" s="167"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="168"/>
+      <c r="K33" s="139">
+        <f>SUM(K6:K32)</f>
+        <v>1.7500000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="114" t="s">
+        <v>960</v>
+      </c>
+      <c r="B34" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="C34" s="170"/>
+      <c r="D34" s="166" t="s">
+        <v>844</v>
+      </c>
+      <c r="E34" s="139">
+        <f>SUM(E6:E33)</f>
+        <v>2.8200000000000003</v>
+      </c>
+      <c r="F34" s="225"/>
+      <c r="G34" s="166" t="s">
+        <v>844</v>
+      </c>
+      <c r="H34" s="139">
+        <f>SUM(H6:H33)</f>
+        <v>1.9700000000000004</v>
+      </c>
+      <c r="I34" s="171"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="178"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="166" t="s">
+        <v>844</v>
+      </c>
+      <c r="B35" s="139">
+        <f>SUM(B6:B34)</f>
+        <v>1.4900000000000007</v>
+      </c>
+      <c r="C35" s="170"/>
+      <c r="D35" s="178"/>
+      <c r="E35" s="178"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="178"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="171"/>
+      <c r="J35" s="171"/>
+      <c r="K35" s="171"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F7:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A6:H6"/>
+  <mergeCells count="10">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C5:C35"/>
+    <mergeCell ref="F5:F35"/>
+    <mergeCell ref="J34:K35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="I5:I35"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -14520,6 +15312,1106 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr defaultRowHeight="23.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="10" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67" t="s">
+        <v>905</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>906</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>907</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>908</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>909</v>
+      </c>
+      <c r="F1" s="69" t="s">
+        <v>910</v>
+      </c>
+      <c r="G1" s="70" t="s">
+        <v>911</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
+        <v>942</v>
+      </c>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="66">
+        <v>5092.3999999999996</v>
+      </c>
+      <c r="F2" s="66">
+        <v>4104.6000000000004</v>
+      </c>
+      <c r="G2" s="66">
+        <f>E2+F2</f>
+        <v>9197</v>
+      </c>
+      <c r="I2" s="61" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" s="62">
+        <v>9197</v>
+      </c>
+      <c r="L2" s="72">
+        <f>G2-J2</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>9779.2999999999993</v>
+      </c>
+      <c r="P2" s="78">
+        <f t="shared" ref="P2:P29" si="0">J2-N2</f>
+        <v>-582.29999999999927</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="63" t="s">
+        <v>885</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>912</v>
+      </c>
+      <c r="C3" s="66">
+        <v>0</v>
+      </c>
+      <c r="D3" s="66">
+        <v>0</v>
+      </c>
+      <c r="E3" s="66">
+        <v>7</v>
+      </c>
+      <c r="F3" s="66">
+        <v>7</v>
+      </c>
+      <c r="G3" s="66">
+        <f>E3+F3</f>
+        <v>14</v>
+      </c>
+      <c r="I3" s="59" t="s">
+        <v>363</v>
+      </c>
+      <c r="J3" s="60">
+        <v>14</v>
+      </c>
+      <c r="L3" s="72">
+        <f t="shared" ref="L3:L31" si="1">G3-J3</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>8.4</v>
+      </c>
+      <c r="P3" s="78">
+        <f t="shared" si="0"/>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="63" t="s">
+        <v>886</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>913</v>
+      </c>
+      <c r="C4" s="66">
+        <v>0</v>
+      </c>
+      <c r="D4" s="66">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4" s="66">
+        <v>18.7</v>
+      </c>
+      <c r="F4" s="66">
+        <v>30.7</v>
+      </c>
+      <c r="G4" s="66">
+        <f t="shared" ref="G4:G31" si="2">E4+F4</f>
+        <v>49.4</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="J4" s="62">
+        <v>49.4</v>
+      </c>
+      <c r="L4" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>55.3</v>
+      </c>
+      <c r="P4" s="78">
+        <f t="shared" si="0"/>
+        <v>-5.8999999999999986</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="63" t="s">
+        <v>887</v>
+      </c>
+      <c r="B5" s="64" t="s">
+        <v>914</v>
+      </c>
+      <c r="C5" s="66">
+        <v>0</v>
+      </c>
+      <c r="D5" s="66">
+        <v>0</v>
+      </c>
+      <c r="E5" s="66">
+        <v>8.4</v>
+      </c>
+      <c r="F5" s="66">
+        <v>24.4</v>
+      </c>
+      <c r="G5" s="66">
+        <f t="shared" si="2"/>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="I5" s="59" t="s">
+        <v>373</v>
+      </c>
+      <c r="J5" s="60">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="L5" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="P5" s="78">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="63" t="s">
+        <v>888</v>
+      </c>
+      <c r="B6" s="64" t="s">
+        <v>915</v>
+      </c>
+      <c r="C6" s="66">
+        <v>0</v>
+      </c>
+      <c r="D6" s="66">
+        <v>0</v>
+      </c>
+      <c r="E6" s="66">
+        <v>4</v>
+      </c>
+      <c r="F6" s="66">
+        <v>3.9</v>
+      </c>
+      <c r="G6" s="66">
+        <f t="shared" si="2"/>
+        <v>7.9</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="J6" s="62">
+        <v>7.9</v>
+      </c>
+      <c r="L6" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>10.1</v>
+      </c>
+      <c r="P6" s="78">
+        <f t="shared" si="0"/>
+        <v>-2.1999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="63" t="s">
+        <v>889</v>
+      </c>
+      <c r="B7" s="64" t="s">
+        <v>916</v>
+      </c>
+      <c r="C7" s="66">
+        <v>0</v>
+      </c>
+      <c r="D7" s="66">
+        <v>9.6</v>
+      </c>
+      <c r="E7" s="66">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F7" s="66">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G7" s="66">
+        <f t="shared" si="2"/>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="I7" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="J7" s="60">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L7" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>23.4</v>
+      </c>
+      <c r="P7" s="78">
+        <f t="shared" si="0"/>
+        <v>-5.2999999999999972</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="63" t="s">
+        <v>890</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>917</v>
+      </c>
+      <c r="C8" s="66">
+        <v>0</v>
+      </c>
+      <c r="D8" s="66">
+        <v>16.7</v>
+      </c>
+      <c r="E8" s="66">
+        <v>15.9</v>
+      </c>
+      <c r="F8" s="66">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="G8" s="66">
+        <f t="shared" si="2"/>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>388</v>
+      </c>
+      <c r="J8" s="62">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="L8" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>43.7</v>
+      </c>
+      <c r="P8" s="78">
+        <f t="shared" si="0"/>
+        <v>-10.900000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="71" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B9" s="64"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="62"/>
+      <c r="L9" s="72"/>
+      <c r="N9">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="P9" s="78">
+        <f t="shared" si="0"/>
+        <v>-78.400000000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="71" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B10" s="64"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="62"/>
+      <c r="L10" s="72"/>
+      <c r="N10">
+        <v>742.1</v>
+      </c>
+      <c r="P10" s="78">
+        <f t="shared" si="0"/>
+        <v>-742.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="63" t="s">
+        <v>918</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>919</v>
+      </c>
+      <c r="C11" s="66">
+        <v>0</v>
+      </c>
+      <c r="D11" s="66">
+        <v>0</v>
+      </c>
+      <c r="E11" s="66">
+        <v>2.8</v>
+      </c>
+      <c r="F11" s="66">
+        <v>2.8</v>
+      </c>
+      <c r="G11" s="66">
+        <f t="shared" si="2"/>
+        <v>5.6</v>
+      </c>
+      <c r="I11" s="59" t="s">
+        <v>393</v>
+      </c>
+      <c r="J11" s="60">
+        <v>5.6</v>
+      </c>
+      <c r="L11" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="78">
+        <f t="shared" si="0"/>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="63" t="s">
+        <v>920</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>921</v>
+      </c>
+      <c r="C12" s="66">
+        <v>0</v>
+      </c>
+      <c r="D12" s="66">
+        <v>229.6</v>
+      </c>
+      <c r="E12" s="66">
+        <v>355.8</v>
+      </c>
+      <c r="F12" s="66">
+        <v>388.9</v>
+      </c>
+      <c r="G12" s="66">
+        <f t="shared" si="2"/>
+        <v>744.7</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="J12" s="62">
+        <v>744.7</v>
+      </c>
+      <c r="L12" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="78">
+        <f t="shared" si="0"/>
+        <v>744.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="63" t="s">
+        <v>891</v>
+      </c>
+      <c r="B13" s="64" t="s">
+        <v>922</v>
+      </c>
+      <c r="C13" s="66">
+        <v>1208</v>
+      </c>
+      <c r="D13" s="66">
+        <v>2697.6</v>
+      </c>
+      <c r="E13" s="66">
+        <v>1957.3</v>
+      </c>
+      <c r="F13" s="66">
+        <v>1990.5</v>
+      </c>
+      <c r="G13" s="66">
+        <f t="shared" si="2"/>
+        <v>3947.8</v>
+      </c>
+      <c r="I13" s="59" t="s">
+        <v>403</v>
+      </c>
+      <c r="J13" s="60">
+        <v>3947.8</v>
+      </c>
+      <c r="L13" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>4000.3</v>
+      </c>
+      <c r="P13" s="78">
+        <f t="shared" si="0"/>
+        <v>-52.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>924</v>
+      </c>
+      <c r="C14" s="66">
+        <v>0</v>
+      </c>
+      <c r="D14" s="66">
+        <v>6.8</v>
+      </c>
+      <c r="E14" s="66">
+        <v>0</v>
+      </c>
+      <c r="F14" s="66">
+        <v>0</v>
+      </c>
+      <c r="G14" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="63" t="s">
+        <v>925</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>926</v>
+      </c>
+      <c r="C15" s="66">
+        <v>0</v>
+      </c>
+      <c r="D15" s="66">
+        <v>89.4</v>
+      </c>
+      <c r="E15" s="66">
+        <v>94.4</v>
+      </c>
+      <c r="F15" s="66">
+        <v>0</v>
+      </c>
+      <c r="G15" s="66">
+        <f t="shared" si="2"/>
+        <v>94.4</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>408</v>
+      </c>
+      <c r="J15" s="62">
+        <v>94.4</v>
+      </c>
+      <c r="L15" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="78">
+        <f t="shared" si="0"/>
+        <v>94.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="63" t="s">
+        <v>892</v>
+      </c>
+      <c r="B16" s="64" t="s">
+        <v>927</v>
+      </c>
+      <c r="C16" s="66">
+        <v>0</v>
+      </c>
+      <c r="D16" s="66">
+        <v>21.1</v>
+      </c>
+      <c r="E16" s="66">
+        <v>0</v>
+      </c>
+      <c r="F16" s="66">
+        <v>0</v>
+      </c>
+      <c r="G16" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="72"/>
+      <c r="P16" s="78"/>
+    </row>
+    <row r="17" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="63" t="s">
+        <v>893</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>928</v>
+      </c>
+      <c r="C17" s="66">
+        <v>0</v>
+      </c>
+      <c r="D17" s="66">
+        <v>0</v>
+      </c>
+      <c r="E17" s="66">
+        <v>0</v>
+      </c>
+      <c r="F17" s="66">
+        <v>24.9</v>
+      </c>
+      <c r="G17" s="66">
+        <f t="shared" si="2"/>
+        <v>24.9</v>
+      </c>
+      <c r="I17" s="59" t="s">
+        <v>413</v>
+      </c>
+      <c r="J17" s="60">
+        <v>24.9</v>
+      </c>
+      <c r="L17" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>23.2</v>
+      </c>
+      <c r="P17" s="78">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="63" t="s">
+        <v>894</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>929</v>
+      </c>
+      <c r="C18" s="66">
+        <v>0</v>
+      </c>
+      <c r="D18" s="66">
+        <v>671.4</v>
+      </c>
+      <c r="E18" s="66">
+        <v>458.6</v>
+      </c>
+      <c r="F18" s="66">
+        <v>191.2</v>
+      </c>
+      <c r="G18" s="66">
+        <f t="shared" si="2"/>
+        <v>649.79999999999995</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="J18" s="62">
+        <v>649.79999999999995</v>
+      </c>
+      <c r="L18" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>239.5</v>
+      </c>
+      <c r="P18" s="78">
+        <f t="shared" si="0"/>
+        <v>410.29999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="63" t="s">
+        <v>895</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>930</v>
+      </c>
+      <c r="C19" s="66">
+        <v>0</v>
+      </c>
+      <c r="D19" s="66">
+        <v>22</v>
+      </c>
+      <c r="E19" s="66">
+        <v>0</v>
+      </c>
+      <c r="F19" s="66">
+        <v>0</v>
+      </c>
+      <c r="G19" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="72"/>
+      <c r="P19" s="78"/>
+    </row>
+    <row r="20" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="63" t="s">
+        <v>896</v>
+      </c>
+      <c r="B20" s="64" t="s">
+        <v>931</v>
+      </c>
+      <c r="C20" s="65">
+        <v>0</v>
+      </c>
+      <c r="D20" s="65">
+        <v>382.5</v>
+      </c>
+      <c r="E20" s="65">
+        <v>201.8</v>
+      </c>
+      <c r="F20" s="65">
+        <v>152</v>
+      </c>
+      <c r="G20" s="66">
+        <f t="shared" si="2"/>
+        <v>353.8</v>
+      </c>
+      <c r="I20" s="59" t="s">
+        <v>531</v>
+      </c>
+      <c r="J20" s="60">
+        <v>353.8</v>
+      </c>
+      <c r="L20" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>365.8</v>
+      </c>
+      <c r="P20" s="78">
+        <f t="shared" si="0"/>
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="B21" s="64" t="s">
+        <v>932</v>
+      </c>
+      <c r="C21" s="65">
+        <v>0</v>
+      </c>
+      <c r="D21" s="65">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="E21" s="65">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="F21" s="65">
+        <v>21</v>
+      </c>
+      <c r="G21" s="66">
+        <f t="shared" si="2"/>
+        <v>59.7</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>539</v>
+      </c>
+      <c r="J21" s="62">
+        <v>59.7</v>
+      </c>
+      <c r="L21" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>48.3</v>
+      </c>
+      <c r="P21" s="78">
+        <f t="shared" si="0"/>
+        <v>11.400000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="63" t="s">
+        <v>898</v>
+      </c>
+      <c r="B22" s="64" t="s">
+        <v>933</v>
+      </c>
+      <c r="C22" s="65">
+        <v>0</v>
+      </c>
+      <c r="D22" s="65">
+        <v>86.2</v>
+      </c>
+      <c r="E22" s="65">
+        <v>64</v>
+      </c>
+      <c r="F22" s="65">
+        <v>43.8</v>
+      </c>
+      <c r="G22" s="66">
+        <f t="shared" si="2"/>
+        <v>107.8</v>
+      </c>
+      <c r="I22" s="59" t="s">
+        <v>546</v>
+      </c>
+      <c r="J22" s="60">
+        <v>107.8</v>
+      </c>
+      <c r="L22" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>91.8</v>
+      </c>
+      <c r="P22" s="78">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="71" t="s">
+        <v>884</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="66"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="77"/>
+      <c r="L23" s="72"/>
+      <c r="N23">
+        <v>11.5</v>
+      </c>
+      <c r="P23" s="78">
+        <f t="shared" si="0"/>
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="71" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="66"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="77"/>
+      <c r="L24" s="72"/>
+      <c r="N24">
+        <v>16.3</v>
+      </c>
+      <c r="P24" s="78">
+        <f t="shared" si="0"/>
+        <v>-16.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="63" t="s">
+        <v>899</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>934</v>
+      </c>
+      <c r="C25" s="66">
+        <v>0</v>
+      </c>
+      <c r="D25" s="66">
+        <v>169.5</v>
+      </c>
+      <c r="E25" s="66">
+        <v>0</v>
+      </c>
+      <c r="F25" s="66">
+        <v>0</v>
+      </c>
+      <c r="G25" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="72"/>
+      <c r="P25" s="78"/>
+    </row>
+    <row r="26" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="63" t="s">
+        <v>900</v>
+      </c>
+      <c r="B26" s="64" t="s">
+        <v>935</v>
+      </c>
+      <c r="C26" s="65">
+        <v>0</v>
+      </c>
+      <c r="D26" s="65">
+        <v>1784.9</v>
+      </c>
+      <c r="E26" s="65">
+        <v>171.1</v>
+      </c>
+      <c r="F26" s="65">
+        <v>125.1</v>
+      </c>
+      <c r="G26" s="66">
+        <f t="shared" si="2"/>
+        <v>296.2</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>553</v>
+      </c>
+      <c r="J26" s="62">
+        <v>296.2</v>
+      </c>
+      <c r="L26" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>302.8</v>
+      </c>
+      <c r="P26" s="78">
+        <f t="shared" si="0"/>
+        <v>-6.6000000000000227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="63" t="s">
+        <v>901</v>
+      </c>
+      <c r="B27" s="64" t="s">
+        <v>936</v>
+      </c>
+      <c r="C27" s="65">
+        <v>0</v>
+      </c>
+      <c r="D27" s="65">
+        <v>204.1</v>
+      </c>
+      <c r="E27" s="65">
+        <v>0</v>
+      </c>
+      <c r="F27" s="65">
+        <v>0</v>
+      </c>
+      <c r="G27" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="63" t="s">
+        <v>902</v>
+      </c>
+      <c r="B28" s="64" t="s">
+        <v>937</v>
+      </c>
+      <c r="C28" s="65">
+        <v>0</v>
+      </c>
+      <c r="D28" s="65">
+        <v>397.1</v>
+      </c>
+      <c r="E28" s="65">
+        <v>400.4</v>
+      </c>
+      <c r="F28" s="65">
+        <v>351.3</v>
+      </c>
+      <c r="G28" s="66">
+        <f t="shared" si="2"/>
+        <v>751.7</v>
+      </c>
+      <c r="I28" s="59" t="s">
+        <v>560</v>
+      </c>
+      <c r="J28" s="60">
+        <v>751.7</v>
+      </c>
+      <c r="L28" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>751.5</v>
+      </c>
+      <c r="P28" s="78">
+        <f t="shared" si="0"/>
+        <v>0.20000000000004547</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="B29" s="64" t="s">
+        <v>938</v>
+      </c>
+      <c r="C29" s="66">
+        <v>0</v>
+      </c>
+      <c r="D29" s="66">
+        <v>24</v>
+      </c>
+      <c r="E29" s="66">
+        <v>11.6</v>
+      </c>
+      <c r="F29" s="66">
+        <v>12.8</v>
+      </c>
+      <c r="G29" s="66">
+        <f t="shared" si="2"/>
+        <v>24.4</v>
+      </c>
+      <c r="L29" s="72">
+        <f t="shared" si="1"/>
+        <v>24.4</v>
+      </c>
+      <c r="N29">
+        <v>24.5</v>
+      </c>
+      <c r="P29" s="78">
+        <f t="shared" si="0"/>
+        <v>-24.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="63" t="s">
+        <v>904</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>939</v>
+      </c>
+      <c r="C30" s="65">
+        <v>0</v>
+      </c>
+      <c r="D30" s="65">
+        <v>4.3</v>
+      </c>
+      <c r="E30" s="65">
+        <v>3.9</v>
+      </c>
+      <c r="F30" s="65">
+        <v>3.9</v>
+      </c>
+      <c r="G30" s="66">
+        <f t="shared" si="2"/>
+        <v>7.8</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>567</v>
+      </c>
+      <c r="J30" s="62">
+        <v>7.8</v>
+      </c>
+      <c r="L30" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="P30" s="78">
+        <f>J30-N30</f>
+        <v>-0.50000000000000089</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="63" t="s">
+        <v>940</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>941</v>
+      </c>
+      <c r="C31" s="66">
+        <v>0</v>
+      </c>
+      <c r="D31" s="66">
+        <v>0</v>
+      </c>
+      <c r="E31" s="66">
+        <v>0</v>
+      </c>
+      <c r="F31" s="66">
+        <v>3.8</v>
+      </c>
+      <c r="G31" s="66">
+        <f t="shared" si="2"/>
+        <v>3.8</v>
+      </c>
+      <c r="L31" s="72">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D269"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18303,7 +20195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -18318,26 +20210,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -18349,12 +20241,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1082</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -18366,12 +20258,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="167" t="s">
         <v>1082</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="141" t="s">
         <v>19</v>
       </c>
@@ -18383,12 +20275,12 @@
       <c r="A5" s="114">
         <v>3</v>
       </c>
-      <c r="B5" s="164" t="s">
+      <c r="B5" s="167" t="s">
         <v>1082</v>
       </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="166"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
       <c r="F5" s="115" t="s">
         <v>19</v>
       </c>
@@ -18400,12 +20292,12 @@
       <c r="A6" s="140">
         <v>4</v>
       </c>
-      <c r="B6" s="182" t="s">
+      <c r="B6" s="185" t="s">
         <v>1082</v>
       </c>
-      <c r="C6" s="183"/>
-      <c r="D6" s="183"/>
-      <c r="E6" s="184"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="186"/>
+      <c r="E6" s="187"/>
       <c r="F6" s="141" t="s">
         <v>19</v>
       </c>
@@ -18427,7 +20319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -18442,26 +20334,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -18473,12 +20365,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1071</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -18490,12 +20382,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="182" t="s">
+      <c r="B4" s="185" t="s">
         <v>1071</v>
       </c>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="184"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="187"/>
       <c r="F4" s="141" t="s">
         <v>19</v>
       </c>
@@ -18515,7 +20407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -18530,26 +20422,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -18561,12 +20453,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1071</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -18579,12 +20471,12 @@
       <c r="A4" s="127">
         <v>2</v>
       </c>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>1077</v>
       </c>
-      <c r="C4" s="188"/>
-      <c r="D4" s="188"/>
-      <c r="E4" s="189"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="192"/>
       <c r="F4" s="128" t="s">
         <v>1076</v>
       </c>
@@ -18593,13 +20485,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
+      <c r="A5" s="176"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
     </row>
     <row r="6" spans="1:7" s="120" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="122" t="s">
@@ -18608,11 +20500,11 @@
       <c r="B6" s="123" t="s">
         <v>1078</v>
       </c>
-      <c r="C6" s="185"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="124">
@@ -18622,11 +20514,11 @@
         <f>7.72-0.525</f>
         <v>7.1949999999999994</v>
       </c>
-      <c r="C7" s="185"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="189"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="124">
@@ -18636,11 +20528,11 @@
         <f>0.6125*3.15-1.8821*1.1*0.25</f>
         <v>1.4117975</v>
       </c>
-      <c r="C8" s="185"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-      <c r="G8" s="186"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="189"/>
+      <c r="E8" s="189"/>
+      <c r="F8" s="189"/>
+      <c r="G8" s="189"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="124">
@@ -18650,11 +20542,11 @@
         <f>0.696*3.15-0.7*2.1*0.12*4</f>
         <v>1.4867999999999997</v>
       </c>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="E9" s="186"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="186"/>
+      <c r="C9" s="188"/>
+      <c r="D9" s="189"/>
+      <c r="E9" s="189"/>
+      <c r="F9" s="189"/>
+      <c r="G9" s="189"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="124">
@@ -18664,11 +20556,11 @@
         <f>0.5625*3.15-0.156</f>
         <v>1.615875</v>
       </c>
-      <c r="C10" s="185"/>
-      <c r="D10" s="186"/>
-      <c r="E10" s="186"/>
-      <c r="F10" s="186"/>
-      <c r="G10" s="186"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="189"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="189"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="124">
@@ -18678,11 +20570,11 @@
         <f>0.4188*3.15--0.7*2.1*0.12*2</f>
         <v>1.6720200000000001</v>
       </c>
-      <c r="C11" s="185"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="186"/>
-      <c r="F11" s="186"/>
-      <c r="G11" s="186"/>
+      <c r="C11" s="188"/>
+      <c r="D11" s="189"/>
+      <c r="E11" s="189"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="189"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="124">
@@ -18692,11 +20584,11 @@
         <f>0.45*3.15-1*2.2*0.25</f>
         <v>0.86749999999999994</v>
       </c>
-      <c r="C12" s="185"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
+      <c r="C12" s="188"/>
+      <c r="D12" s="189"/>
+      <c r="E12" s="189"/>
+      <c r="F12" s="189"/>
+      <c r="G12" s="189"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="124">
@@ -18706,11 +20598,11 @@
         <f>0.125*3.15+0.0375*3.15</f>
         <v>0.51187499999999997</v>
       </c>
-      <c r="C13" s="185"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
-      <c r="F13" s="186"/>
-      <c r="G13" s="186"/>
+      <c r="C13" s="188"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+      <c r="F13" s="189"/>
+      <c r="G13" s="189"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="134">
@@ -18720,11 +20612,11 @@
         <f>0.45*3.15-1*2.2*0.25</f>
         <v>0.86749999999999994</v>
       </c>
-      <c r="C14" s="185"/>
-      <c r="D14" s="186"/>
-      <c r="E14" s="186"/>
-      <c r="F14" s="186"/>
-      <c r="G14" s="186"/>
+      <c r="C14" s="188"/>
+      <c r="D14" s="189"/>
+      <c r="E14" s="189"/>
+      <c r="F14" s="189"/>
+      <c r="G14" s="189"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="134">
@@ -18734,11 +20626,11 @@
         <f>3.9*3.15*0.25-0.25*2.1</f>
         <v>2.5462500000000001</v>
       </c>
-      <c r="C15" s="185"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="186"/>
-      <c r="G15" s="186"/>
+      <c r="C15" s="188"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="189"/>
+      <c r="G15" s="189"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="134">
@@ -18748,11 +20640,11 @@
         <f>0.9875*3.15-0.294*2.1+0.4*3.15-0.03</f>
         <v>3.7232250000000007</v>
       </c>
-      <c r="C16" s="185"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="186"/>
+      <c r="C16" s="188"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
+      <c r="F16" s="189"/>
+      <c r="G16" s="189"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="114" t="s">
@@ -18762,11 +20654,11 @@
         <f>SUM(B7:B16)</f>
         <v>21.897842499999996</v>
       </c>
-      <c r="C17" s="185"/>
-      <c r="D17" s="186"/>
-      <c r="E17" s="186"/>
-      <c r="F17" s="186"/>
-      <c r="G17" s="186"/>
+      <c r="C17" s="188"/>
+      <c r="D17" s="189"/>
+      <c r="E17" s="189"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -18785,7 +20677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -18804,19 +20696,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="172"/>
     </row>
     <row r="2" spans="1:11" s="119" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -18825,17 +20717,17 @@
       <c r="B2" s="37" t="s">
         <v>1080</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="170" t="s">
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="173" t="s">
         <v>814</v>
       </c>
-      <c r="H2" s="171"/>
-      <c r="I2" s="172"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="175"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -18850,17 +20742,17 @@
       <c r="B3" s="114">
         <v>72</v>
       </c>
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="167" t="s">
         <v>1073</v>
       </c>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="190" t="s">
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="193" t="s">
         <v>1072</v>
       </c>
-      <c r="H3" s="191"/>
-      <c r="I3" s="192"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="195"/>
       <c r="J3" s="115" t="s">
         <v>15</v>
       </c>
@@ -18875,17 +20767,17 @@
       <c r="B4" s="127">
         <v>78</v>
       </c>
-      <c r="C4" s="187" t="s">
+      <c r="C4" s="190" t="s">
         <v>1073</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="193" t="s">
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="196" t="s">
         <v>1074</v>
       </c>
-      <c r="H4" s="194"/>
-      <c r="I4" s="195"/>
+      <c r="H4" s="197"/>
+      <c r="I4" s="198"/>
       <c r="J4" s="128" t="s">
         <v>15</v>
       </c>
@@ -18900,17 +20792,17 @@
       <c r="B5" s="114">
         <v>84</v>
       </c>
-      <c r="C5" s="164" t="s">
+      <c r="C5" s="167" t="s">
         <v>1073</v>
       </c>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="190" t="s">
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="193" t="s">
         <v>1072</v>
       </c>
-      <c r="H5" s="191"/>
-      <c r="I5" s="192"/>
+      <c r="H5" s="194"/>
+      <c r="I5" s="195"/>
       <c r="J5" s="115" t="s">
         <v>15</v>
       </c>
@@ -18925,17 +20817,17 @@
       <c r="B6" s="127">
         <v>90</v>
       </c>
-      <c r="C6" s="187" t="s">
+      <c r="C6" s="190" t="s">
         <v>1073</v>
       </c>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="189"/>
-      <c r="G6" s="193" t="s">
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="192"/>
+      <c r="G6" s="196" t="s">
         <v>1074</v>
       </c>
-      <c r="H6" s="194"/>
-      <c r="I6" s="195"/>
+      <c r="H6" s="197"/>
+      <c r="I6" s="198"/>
       <c r="J6" s="128" t="s">
         <v>15</v>
       </c>
@@ -18950,17 +20842,17 @@
       <c r="B7" s="114">
         <v>96</v>
       </c>
-      <c r="C7" s="164" t="s">
+      <c r="C7" s="167" t="s">
         <v>1073</v>
       </c>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="166"/>
-      <c r="G7" s="190" t="s">
+      <c r="D7" s="168"/>
+      <c r="E7" s="168"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="193" t="s">
         <v>1072</v>
       </c>
-      <c r="H7" s="191"/>
-      <c r="I7" s="192"/>
+      <c r="H7" s="194"/>
+      <c r="I7" s="195"/>
       <c r="J7" s="115" t="s">
         <v>15</v>
       </c>
@@ -18975,17 +20867,17 @@
       <c r="B8" s="127">
         <v>102</v>
       </c>
-      <c r="C8" s="187" t="s">
+      <c r="C8" s="190" t="s">
         <v>1073</v>
       </c>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="189"/>
-      <c r="G8" s="193" t="s">
+      <c r="D8" s="191"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="192"/>
+      <c r="G8" s="196" t="s">
         <v>1074</v>
       </c>
-      <c r="H8" s="194"/>
-      <c r="I8" s="195"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="198"/>
       <c r="J8" s="128" t="s">
         <v>15</v>
       </c>
@@ -18994,17 +20886,17 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="173"/>
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="173"/>
-      <c r="H9" s="173"/>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
+      <c r="A9" s="176"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="176"/>
+      <c r="K9" s="176"/>
     </row>
     <row r="10" spans="1:11" s="120" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="122" t="s">
@@ -19016,7 +20908,7 @@
       <c r="C10" s="130" t="s">
         <v>1075</v>
       </c>
-      <c r="D10" s="199"/>
+      <c r="D10" s="202"/>
       <c r="E10" s="123" t="s">
         <v>830</v>
       </c>
@@ -19026,10 +20918,10 @@
       <c r="G10" s="130" t="s">
         <v>1075</v>
       </c>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196"/>
-      <c r="J10" s="196"/>
-      <c r="K10" s="196"/>
+      <c r="H10" s="199"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="199"/>
+      <c r="K10" s="199"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="124">
@@ -19041,7 +20933,7 @@
       <c r="C11" s="125">
         <v>3.24</v>
       </c>
-      <c r="D11" s="199"/>
+      <c r="D11" s="202"/>
       <c r="E11" s="121">
         <v>28</v>
       </c>
@@ -19051,10 +20943,10 @@
       <c r="G11" s="125">
         <v>19.399999999999999</v>
       </c>
-      <c r="H11" s="196"/>
-      <c r="I11" s="196"/>
-      <c r="J11" s="196"/>
-      <c r="K11" s="196"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="199"/>
+      <c r="K11" s="199"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="124">
@@ -19066,7 +20958,7 @@
       <c r="C12" s="125">
         <v>34.08</v>
       </c>
-      <c r="D12" s="199"/>
+      <c r="D12" s="202"/>
       <c r="E12" s="121">
         <v>29</v>
       </c>
@@ -19076,10 +20968,10 @@
       <c r="G12" s="125">
         <v>19.399999999999999</v>
       </c>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196"/>
-      <c r="J12" s="196"/>
-      <c r="K12" s="196"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="199"/>
+      <c r="K12" s="199"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="124">
@@ -19091,7 +20983,7 @@
       <c r="C13" s="125">
         <v>7.68</v>
       </c>
-      <c r="D13" s="199"/>
+      <c r="D13" s="202"/>
       <c r="E13" s="121">
         <v>30</v>
       </c>
@@ -19101,10 +20993,10 @@
       <c r="G13" s="125">
         <v>48.199999999999996</v>
       </c>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
-      <c r="J13" s="196"/>
-      <c r="K13" s="196"/>
+      <c r="H13" s="199"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="199"/>
+      <c r="K13" s="199"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="124">
@@ -19116,7 +21008,7 @@
       <c r="C14" s="125">
         <v>17.16</v>
       </c>
-      <c r="D14" s="199"/>
+      <c r="D14" s="202"/>
       <c r="E14" s="121">
         <v>31</v>
       </c>
@@ -19126,10 +21018,10 @@
       <c r="G14" s="125">
         <v>35</v>
       </c>
-      <c r="H14" s="196"/>
-      <c r="I14" s="196"/>
-      <c r="J14" s="196"/>
-      <c r="K14" s="196"/>
+      <c r="H14" s="199"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="199"/>
+      <c r="K14" s="199"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="124">
@@ -19141,7 +21033,7 @@
       <c r="C15" s="125">
         <v>32.4</v>
       </c>
-      <c r="D15" s="199"/>
+      <c r="D15" s="202"/>
       <c r="E15" s="121">
         <v>32</v>
       </c>
@@ -19151,10 +21043,10 @@
       <c r="G15" s="125">
         <v>18.2</v>
       </c>
-      <c r="H15" s="196"/>
-      <c r="I15" s="196"/>
-      <c r="J15" s="196"/>
-      <c r="K15" s="196"/>
+      <c r="H15" s="199"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="199"/>
+      <c r="K15" s="199"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="124">
@@ -19166,7 +21058,7 @@
       <c r="C16" s="125">
         <v>19.2</v>
       </c>
-      <c r="D16" s="199"/>
+      <c r="D16" s="202"/>
       <c r="E16" s="121">
         <v>33</v>
       </c>
@@ -19176,10 +21068,10 @@
       <c r="G16" s="125">
         <v>9.1999999999999993</v>
       </c>
-      <c r="H16" s="196"/>
-      <c r="I16" s="196"/>
-      <c r="J16" s="196"/>
-      <c r="K16" s="196"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="199"/>
+      <c r="J16" s="199"/>
+      <c r="K16" s="199"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="124">
@@ -19191,7 +21083,7 @@
       <c r="C17" s="125">
         <v>32.4</v>
       </c>
-      <c r="D17" s="199"/>
+      <c r="D17" s="202"/>
       <c r="E17" s="121">
         <v>34</v>
       </c>
@@ -19201,10 +21093,10 @@
       <c r="G17" s="125">
         <v>21.8</v>
       </c>
-      <c r="H17" s="196"/>
-      <c r="I17" s="196"/>
-      <c r="J17" s="196"/>
-      <c r="K17" s="196"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="199"/>
+      <c r="K17" s="199"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="124">
@@ -19216,7 +21108,7 @@
       <c r="C18" s="125">
         <v>49.199999999999996</v>
       </c>
-      <c r="D18" s="199"/>
+      <c r="D18" s="202"/>
       <c r="E18" s="121">
         <v>35</v>
       </c>
@@ -19226,10 +21118,10 @@
       <c r="G18" s="125">
         <v>24.2</v>
       </c>
-      <c r="H18" s="196"/>
-      <c r="I18" s="196"/>
-      <c r="J18" s="196"/>
-      <c r="K18" s="196"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="199"/>
+      <c r="K18" s="199"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="124">
@@ -19241,7 +21133,7 @@
       <c r="C19" s="125">
         <v>15.6</v>
       </c>
-      <c r="D19" s="199"/>
+      <c r="D19" s="202"/>
       <c r="E19" s="121">
         <v>36</v>
       </c>
@@ -19251,10 +21143,10 @@
       <c r="G19" s="125">
         <v>42.199999999999996</v>
       </c>
-      <c r="H19" s="196"/>
-      <c r="I19" s="196"/>
-      <c r="J19" s="196"/>
-      <c r="K19" s="196"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="199"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="124">
@@ -19266,7 +21158,7 @@
       <c r="C20" s="125">
         <v>21.599999999999998</v>
       </c>
-      <c r="D20" s="199"/>
+      <c r="D20" s="202"/>
       <c r="E20" s="121">
         <v>37</v>
       </c>
@@ -19276,10 +21168,10 @@
       <c r="G20" s="125">
         <v>1.7599999999999998</v>
       </c>
-      <c r="H20" s="196"/>
-      <c r="I20" s="196"/>
-      <c r="J20" s="196"/>
-      <c r="K20" s="196"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="199"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="124">
@@ -19291,7 +21183,7 @@
       <c r="C21" s="125">
         <v>8.4</v>
       </c>
-      <c r="D21" s="199"/>
+      <c r="D21" s="202"/>
       <c r="E21" s="121">
         <v>38</v>
       </c>
@@ -19301,10 +21193,10 @@
       <c r="G21" s="125">
         <v>29</v>
       </c>
-      <c r="H21" s="196"/>
-      <c r="I21" s="196"/>
-      <c r="J21" s="196"/>
-      <c r="K21" s="196"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="199"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="124">
@@ -19316,7 +21208,7 @@
       <c r="C22" s="125">
         <v>4.8</v>
       </c>
-      <c r="D22" s="199"/>
+      <c r="D22" s="202"/>
       <c r="E22" s="121">
         <v>39</v>
       </c>
@@ -19326,10 +21218,10 @@
       <c r="G22" s="125">
         <v>23</v>
       </c>
-      <c r="H22" s="196"/>
-      <c r="I22" s="196"/>
-      <c r="J22" s="196"/>
-      <c r="K22" s="196"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="124">
@@ -19341,7 +21233,7 @@
       <c r="C23" s="125">
         <v>20.04</v>
       </c>
-      <c r="D23" s="199"/>
+      <c r="D23" s="202"/>
       <c r="E23" s="121">
         <v>40</v>
       </c>
@@ -19351,10 +21243,10 @@
       <c r="G23" s="125">
         <v>14.839999999999998</v>
       </c>
-      <c r="H23" s="196"/>
-      <c r="I23" s="196"/>
-      <c r="J23" s="196"/>
-      <c r="K23" s="196"/>
+      <c r="H23" s="199"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="199"/>
+      <c r="K23" s="199"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="124">
@@ -19366,7 +21258,7 @@
       <c r="C24" s="125">
         <v>19.2</v>
       </c>
-      <c r="D24" s="199"/>
+      <c r="D24" s="202"/>
       <c r="E24" s="121">
         <v>41</v>
       </c>
@@ -19376,10 +21268,10 @@
       <c r="G24" s="125">
         <v>2.5999999999999996</v>
       </c>
-      <c r="H24" s="196"/>
-      <c r="I24" s="196"/>
-      <c r="J24" s="196"/>
-      <c r="K24" s="196"/>
+      <c r="H24" s="199"/>
+      <c r="I24" s="199"/>
+      <c r="J24" s="199"/>
+      <c r="K24" s="199"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="124">
@@ -19391,7 +21283,7 @@
       <c r="C25" s="125">
         <v>42</v>
       </c>
-      <c r="D25" s="199"/>
+      <c r="D25" s="202"/>
       <c r="E25" s="121">
         <v>42</v>
       </c>
@@ -19401,10 +21293,10 @@
       <c r="G25" s="125">
         <v>27.4</v>
       </c>
-      <c r="H25" s="196"/>
-      <c r="I25" s="196"/>
-      <c r="J25" s="196"/>
-      <c r="K25" s="196"/>
+      <c r="H25" s="199"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="199"/>
+      <c r="K25" s="199"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="124">
@@ -19416,7 +21308,7 @@
       <c r="C26" s="125">
         <v>27.599999999999998</v>
       </c>
-      <c r="D26" s="199"/>
+      <c r="D26" s="202"/>
       <c r="E26" s="121">
         <v>43</v>
       </c>
@@ -19426,10 +21318,10 @@
       <c r="G26" s="125">
         <v>19.399999999999999</v>
       </c>
-      <c r="H26" s="196"/>
-      <c r="I26" s="196"/>
-      <c r="J26" s="196"/>
-      <c r="K26" s="196"/>
+      <c r="H26" s="199"/>
+      <c r="I26" s="199"/>
+      <c r="J26" s="199"/>
+      <c r="K26" s="199"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="124">
@@ -19441,7 +21333,7 @@
       <c r="C27" s="125">
         <v>26.4</v>
       </c>
-      <c r="D27" s="199"/>
+      <c r="D27" s="202"/>
       <c r="E27" s="121">
         <v>44</v>
       </c>
@@ -19451,10 +21343,10 @@
       <c r="G27" s="126">
         <v>4.5</v>
       </c>
-      <c r="H27" s="196"/>
-      <c r="I27" s="196"/>
-      <c r="J27" s="196"/>
-      <c r="K27" s="196"/>
+      <c r="H27" s="199"/>
+      <c r="I27" s="199"/>
+      <c r="J27" s="199"/>
+      <c r="K27" s="199"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="124">
@@ -19466,7 +21358,7 @@
       <c r="C28" s="125">
         <v>16.8</v>
       </c>
-      <c r="D28" s="199"/>
+      <c r="D28" s="202"/>
       <c r="E28" s="121">
         <v>45</v>
       </c>
@@ -19476,10 +21368,10 @@
       <c r="G28" s="125">
         <v>6.4399999999999995</v>
       </c>
-      <c r="H28" s="196"/>
-      <c r="I28" s="196"/>
-      <c r="J28" s="196"/>
-      <c r="K28" s="196"/>
+      <c r="H28" s="199"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="199"/>
+      <c r="K28" s="199"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="124">
@@ -19491,7 +21383,7 @@
       <c r="C29" s="125">
         <v>8.4</v>
       </c>
-      <c r="D29" s="199"/>
+      <c r="D29" s="202"/>
       <c r="E29" s="121">
         <v>46</v>
       </c>
@@ -19501,10 +21393,10 @@
       <c r="G29" s="125">
         <v>30.2</v>
       </c>
-      <c r="H29" s="196"/>
-      <c r="I29" s="196"/>
-      <c r="J29" s="196"/>
-      <c r="K29" s="196"/>
+      <c r="H29" s="199"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="199"/>
+      <c r="K29" s="199"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="124">
@@ -19516,7 +21408,7 @@
       <c r="C30" s="125">
         <v>108</v>
       </c>
-      <c r="D30" s="199"/>
+      <c r="D30" s="202"/>
       <c r="E30" s="121">
         <v>47</v>
       </c>
@@ -19526,10 +21418,10 @@
       <c r="G30" s="125">
         <v>23.24</v>
       </c>
-      <c r="H30" s="196"/>
-      <c r="I30" s="196"/>
-      <c r="J30" s="196"/>
-      <c r="K30" s="196"/>
+      <c r="H30" s="199"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="199"/>
+      <c r="K30" s="199"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="124">
@@ -19541,7 +21433,7 @@
       <c r="C31" s="125">
         <v>12.360000000000001</v>
       </c>
-      <c r="D31" s="199"/>
+      <c r="D31" s="202"/>
       <c r="E31" s="121">
         <v>48</v>
       </c>
@@ -19551,10 +21443,10 @@
       <c r="G31" s="125">
         <v>5.24</v>
       </c>
-      <c r="H31" s="196"/>
-      <c r="I31" s="196"/>
-      <c r="J31" s="196"/>
-      <c r="K31" s="196"/>
+      <c r="H31" s="199"/>
+      <c r="I31" s="199"/>
+      <c r="J31" s="199"/>
+      <c r="K31" s="199"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="124">
@@ -19566,7 +21458,7 @@
       <c r="C32" s="125">
         <v>7.68</v>
       </c>
-      <c r="D32" s="199"/>
+      <c r="D32" s="202"/>
       <c r="E32" s="121">
         <v>49</v>
       </c>
@@ -19576,10 +21468,10 @@
       <c r="G32" s="125">
         <v>9.7999999999999989</v>
       </c>
-      <c r="H32" s="196"/>
-      <c r="I32" s="196"/>
-      <c r="J32" s="196"/>
-      <c r="K32" s="196"/>
+      <c r="H32" s="199"/>
+      <c r="I32" s="199"/>
+      <c r="J32" s="199"/>
+      <c r="K32" s="199"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="124">
@@ -19591,7 +21483,7 @@
       <c r="C33" s="125">
         <v>36</v>
       </c>
-      <c r="D33" s="199"/>
+      <c r="D33" s="202"/>
       <c r="E33" s="121">
         <v>50</v>
       </c>
@@ -19601,10 +21493,10 @@
       <c r="G33" s="125">
         <v>9.7999999999999989</v>
       </c>
-      <c r="H33" s="196"/>
-      <c r="I33" s="196"/>
-      <c r="J33" s="196"/>
-      <c r="K33" s="196"/>
+      <c r="H33" s="199"/>
+      <c r="I33" s="199"/>
+      <c r="J33" s="199"/>
+      <c r="K33" s="199"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="138"/>
@@ -19613,7 +21505,7 @@
         <f>SUM(C11:C33)</f>
         <v>570.24</v>
       </c>
-      <c r="D34" s="199"/>
+      <c r="D34" s="202"/>
       <c r="E34" s="121">
         <v>51</v>
       </c>
@@ -19623,16 +21515,16 @@
       <c r="G34" s="125">
         <v>20.599999999999998</v>
       </c>
-      <c r="H34" s="196"/>
-      <c r="I34" s="196"/>
-      <c r="J34" s="196"/>
-      <c r="K34" s="196"/>
+      <c r="H34" s="199"/>
+      <c r="I34" s="199"/>
+      <c r="J34" s="199"/>
+      <c r="K34" s="199"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="200"/>
-      <c r="B35" s="200"/>
-      <c r="C35" s="200"/>
-      <c r="D35" s="199"/>
+      <c r="A35" s="203"/>
+      <c r="B35" s="203"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="202"/>
       <c r="E35" s="121">
         <v>52</v>
       </c>
@@ -19642,16 +21534,16 @@
       <c r="G35" s="125">
         <v>8.6</v>
       </c>
-      <c r="H35" s="196"/>
-      <c r="I35" s="196"/>
-      <c r="J35" s="196"/>
-      <c r="K35" s="196"/>
+      <c r="H35" s="199"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="199"/>
+      <c r="K35" s="199"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="200"/>
-      <c r="B36" s="200"/>
-      <c r="C36" s="200"/>
-      <c r="D36" s="199"/>
+      <c r="A36" s="203"/>
+      <c r="B36" s="203"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="202"/>
       <c r="E36" s="121">
         <v>54</v>
       </c>
@@ -19661,16 +21553,16 @@
       <c r="G36" s="125">
         <v>9.7999999999999989</v>
       </c>
-      <c r="H36" s="196"/>
-      <c r="I36" s="196"/>
-      <c r="J36" s="196"/>
-      <c r="K36" s="196"/>
+      <c r="H36" s="199"/>
+      <c r="I36" s="199"/>
+      <c r="J36" s="199"/>
+      <c r="K36" s="199"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="200"/>
-      <c r="B37" s="200"/>
-      <c r="C37" s="200"/>
-      <c r="D37" s="199"/>
+      <c r="A37" s="203"/>
+      <c r="B37" s="203"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="202"/>
       <c r="E37" s="121">
         <v>55</v>
       </c>
@@ -19680,44 +21572,44 @@
       <c r="G37" s="125">
         <v>7.6400000000000006</v>
       </c>
-      <c r="H37" s="196"/>
-      <c r="I37" s="196"/>
-      <c r="J37" s="196"/>
-      <c r="K37" s="196"/>
+      <c r="H37" s="199"/>
+      <c r="I37" s="199"/>
+      <c r="J37" s="199"/>
+      <c r="K37" s="199"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="197"/>
-      <c r="B38" s="197"/>
-      <c r="C38" s="197"/>
-      <c r="D38" s="197"/>
-      <c r="E38" s="197"/>
-      <c r="F38" s="198"/>
+      <c r="A38" s="200"/>
+      <c r="B38" s="200"/>
+      <c r="C38" s="200"/>
+      <c r="D38" s="200"/>
+      <c r="E38" s="200"/>
+      <c r="F38" s="201"/>
       <c r="G38" s="125">
         <f>SUM(G11:G37)</f>
         <v>491.46</v>
       </c>
-      <c r="H38" s="196"/>
-      <c r="I38" s="196"/>
-      <c r="J38" s="196"/>
-      <c r="K38" s="196"/>
+      <c r="H38" s="199"/>
+      <c r="I38" s="199"/>
+      <c r="J38" s="199"/>
+      <c r="K38" s="199"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="201" t="s">
+      <c r="A39" s="204" t="s">
         <v>1081</v>
       </c>
-      <c r="B39" s="201"/>
-      <c r="C39" s="201"/>
+      <c r="B39" s="204"/>
+      <c r="C39" s="204"/>
       <c r="D39" s="139">
         <f>C34+G38</f>
         <v>1061.7</v>
       </c>
-      <c r="E39" s="167"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="196"/>
-      <c r="I39" s="196"/>
-      <c r="J39" s="196"/>
-      <c r="K39" s="196"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="199"/>
+      <c r="G39" s="199"/>
+      <c r="H39" s="199"/>
+      <c r="I39" s="199"/>
+      <c r="J39" s="199"/>
+      <c r="K39" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -19749,7 +21641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -19768,17 +21660,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -19786,18 +21678,18 @@
       <c r="A2" s="36" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="208" t="s">
+      <c r="B2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211" t="s">
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>814</v>
       </c>
-      <c r="I2" s="212"/>
+      <c r="I2" s="215"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -19809,16 +21701,16 @@
       <c r="A3" s="107">
         <v>1</v>
       </c>
-      <c r="B3" s="203"/>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="206" t="s">
+      <c r="B3" s="206"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="207"/>
+      <c r="I3" s="210"/>
       <c r="J3" s="107" t="s">
         <v>15</v>
       </c>
@@ -19828,35 +21720,35 @@
       <c r="A4" s="107">
         <v>2</v>
       </c>
-      <c r="B4" s="203">
+      <c r="B4" s="206">
         <v>2</v>
       </c>
-      <c r="C4" s="204"/>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="206" t="s">
+      <c r="C4" s="207"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="209" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="207"/>
+      <c r="I4" s="210"/>
       <c r="J4" s="107" t="s">
         <v>15</v>
       </c>
       <c r="K4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="202"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202"/>
-      <c r="K5" s="202"/>
+      <c r="A5" s="205"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
     </row>
     <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
@@ -20374,7 +22266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -20393,30 +22285,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="217" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
     </row>
     <row r="2" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="213" t="s">
+      <c r="B2" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
+      <c r="C2" s="216"/>
+      <c r="D2" s="216"/>
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
       <c r="G2" s="79" t="s">
         <v>814</v>
       </c>
@@ -20432,13 +22324,13 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="216" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="213"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="216"/>
       <c r="G3" s="88" t="s">
         <v>418</v>
       </c>
@@ -20457,13 +22349,13 @@
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
       <c r="G4" s="100" t="s">
         <v>531</v>
       </c>
@@ -20476,17 +22368,17 @@
       </c>
       <c r="J4" s="100"/>
     </row>
-    <row r="5" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="79">
         <v>3</v>
       </c>
-      <c r="B5" s="213" t="s">
+      <c r="B5" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="213"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
       <c r="G5" s="88" t="s">
         <v>539</v>
       </c>
@@ -20499,17 +22391,17 @@
       </c>
       <c r="J5" s="100"/>
     </row>
-    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="79">
         <v>4</v>
       </c>
-      <c r="B6" s="213" t="s">
+      <c r="B6" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="213"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="213"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
       <c r="G6" s="100" t="s">
         <v>546</v>
       </c>
@@ -20526,13 +22418,13 @@
       <c r="A7" s="79">
         <v>5</v>
       </c>
-      <c r="B7" s="213" t="s">
+      <c r="B7" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="213"/>
-      <c r="D7" s="213"/>
-      <c r="E7" s="213"/>
-      <c r="F7" s="213"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="216"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
       <c r="G7" s="88" t="s">
         <v>553</v>
       </c>
@@ -20549,13 +22441,13 @@
       <c r="A8" s="79">
         <v>6</v>
       </c>
-      <c r="B8" s="213" t="s">
+      <c r="B8" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C8" s="213"/>
-      <c r="D8" s="213"/>
-      <c r="E8" s="213"/>
-      <c r="F8" s="213"/>
+      <c r="C8" s="216"/>
+      <c r="D8" s="216"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
       <c r="G8" s="100" t="s">
         <v>560</v>
       </c>
@@ -20572,12 +22464,12 @@
       <c r="A9" s="79">
         <v>7</v>
       </c>
-      <c r="B9" s="215" t="s">
+      <c r="B9" s="218" t="s">
         <v>1061</v>
       </c>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="217"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="220"/>
       <c r="F9" s="79" t="s">
         <v>1059</v>
       </c>
@@ -20596,16 +22488,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="218"/>
-      <c r="B10" s="218"/>
-      <c r="C10" s="218"/>
-      <c r="D10" s="218"/>
-      <c r="E10" s="218"/>
-      <c r="F10" s="218"/>
-      <c r="G10" s="218"/>
-      <c r="H10" s="218"/>
-      <c r="I10" s="218"/>
-      <c r="J10" s="219"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="221"/>
+      <c r="C10" s="221"/>
+      <c r="D10" s="221"/>
+      <c r="E10" s="221"/>
+      <c r="F10" s="221"/>
+      <c r="G10" s="221"/>
+      <c r="H10" s="221"/>
+      <c r="I10" s="221"/>
+      <c r="J10" s="222"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -20620,7 +22512,7 @@
       <c r="D11" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="E11" s="221"/>
+      <c r="E11" s="224"/>
       <c r="F11" s="79" t="s">
         <v>1055</v>
       </c>
@@ -20633,7 +22525,7 @@
       <c r="I11" s="79" t="s">
         <v>831</v>
       </c>
-      <c r="J11" s="220"/>
+      <c r="J11" s="223"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="92">
@@ -20648,7 +22540,7 @@
       <c r="D12" s="95">
         <v>11.7</v>
       </c>
-      <c r="E12" s="221"/>
+      <c r="E12" s="224"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -20661,7 +22553,7 @@
       <c r="I12" s="93">
         <v>33</v>
       </c>
-      <c r="J12" s="220"/>
+      <c r="J12" s="223"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="102">
@@ -20676,7 +22568,7 @@
       <c r="D13" s="101">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E13" s="221"/>
+      <c r="E13" s="224"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -20689,7 +22581,7 @@
       <c r="I13" s="93">
         <v>14.1</v>
       </c>
-      <c r="J13" s="220"/>
+      <c r="J13" s="223"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="92">
@@ -20704,7 +22596,7 @@
       <c r="D14" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E14" s="221"/>
+      <c r="E14" s="224"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -20717,7 +22609,7 @@
       <c r="I14" s="93">
         <v>8.1</v>
       </c>
-      <c r="J14" s="220"/>
+      <c r="J14" s="223"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="102">
@@ -20732,7 +22624,7 @@
       <c r="D15" s="101">
         <v>2.6</v>
       </c>
-      <c r="E15" s="221"/>
+      <c r="E15" s="224"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -20745,7 +22637,7 @@
       <c r="I15" s="93">
         <v>65.8</v>
       </c>
-      <c r="J15" s="220"/>
+      <c r="J15" s="223"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="92">
@@ -20760,7 +22652,7 @@
       <c r="D16" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E16" s="221"/>
+      <c r="E16" s="224"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -20773,7 +22665,7 @@
       <c r="I16" s="93">
         <v>2.6</v>
       </c>
-      <c r="J16" s="220"/>
+      <c r="J16" s="223"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="92">
@@ -20788,7 +22680,7 @@
       <c r="D17" s="95">
         <v>11.7</v>
       </c>
-      <c r="E17" s="221"/>
+      <c r="E17" s="224"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -20801,7 +22693,7 @@
       <c r="I17" s="93">
         <v>13.6</v>
       </c>
-      <c r="J17" s="220"/>
+      <c r="J17" s="223"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="102">
@@ -20816,7 +22708,7 @@
       <c r="D18" s="101">
         <v>31.6</v>
       </c>
-      <c r="E18" s="221"/>
+      <c r="E18" s="224"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -20829,7 +22721,7 @@
       <c r="I18" s="93">
         <v>5.8</v>
       </c>
-      <c r="J18" s="220"/>
+      <c r="J18" s="223"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="92">
@@ -20844,7 +22736,7 @@
       <c r="D19" s="95">
         <v>5.9</v>
       </c>
-      <c r="E19" s="221"/>
+      <c r="E19" s="224"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -20857,7 +22749,7 @@
       <c r="I19" s="93">
         <v>67.8</v>
       </c>
-      <c r="J19" s="220"/>
+      <c r="J19" s="223"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="92">
@@ -20872,7 +22764,7 @@
       <c r="D20" s="95">
         <v>36.9</v>
       </c>
-      <c r="E20" s="221"/>
+      <c r="E20" s="224"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -20885,7 +22777,7 @@
       <c r="I20" s="93">
         <v>1.8</v>
       </c>
-      <c r="J20" s="220"/>
+      <c r="J20" s="223"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="92">
@@ -20900,7 +22792,7 @@
       <c r="D21" s="95">
         <v>33.9</v>
       </c>
-      <c r="E21" s="221"/>
+      <c r="E21" s="224"/>
       <c r="F21" s="93">
         <v>3</v>
       </c>
@@ -20913,7 +22805,7 @@
       <c r="I21" s="93">
         <v>35.4</v>
       </c>
-      <c r="J21" s="220"/>
+      <c r="J21" s="223"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="92">
@@ -20928,7 +22820,7 @@
       <c r="D22" s="95">
         <v>11.9</v>
       </c>
-      <c r="E22" s="221"/>
+      <c r="E22" s="224"/>
       <c r="F22" s="93">
         <v>3</v>
       </c>
@@ -20941,7 +22833,7 @@
       <c r="I22" s="93">
         <v>5.9</v>
       </c>
-      <c r="J22" s="220"/>
+      <c r="J22" s="223"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="102">
@@ -20956,7 +22848,7 @@
       <c r="D23" s="101">
         <v>5.7</v>
       </c>
-      <c r="E23" s="221"/>
+      <c r="E23" s="224"/>
       <c r="F23" s="93">
         <v>3</v>
       </c>
@@ -20969,7 +22861,7 @@
       <c r="I23" s="93">
         <v>29.5</v>
       </c>
-      <c r="J23" s="220"/>
+      <c r="J23" s="223"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="92">
@@ -20984,7 +22876,7 @@
       <c r="D24" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E24" s="221"/>
+      <c r="E24" s="224"/>
       <c r="F24" s="93">
         <v>3</v>
       </c>
@@ -20997,7 +22889,7 @@
       <c r="I24" s="93">
         <v>36.9</v>
       </c>
-      <c r="J24" s="220"/>
+      <c r="J24" s="223"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="102">
@@ -21012,7 +22904,7 @@
       <c r="D25" s="101">
         <v>1.8</v>
       </c>
-      <c r="E25" s="221"/>
+      <c r="E25" s="224"/>
       <c r="F25" s="93">
         <v>3</v>
       </c>
@@ -21025,7 +22917,7 @@
       <c r="I25" s="93">
         <v>36.5</v>
       </c>
-      <c r="J25" s="220"/>
+      <c r="J25" s="223"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="92">
@@ -21040,7 +22932,7 @@
       <c r="D26" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E26" s="221"/>
+      <c r="E26" s="224"/>
       <c r="F26" s="96">
         <v>3</v>
       </c>
@@ -21053,7 +22945,7 @@
       <c r="I26" s="96">
         <v>29.5</v>
       </c>
-      <c r="J26" s="220"/>
+      <c r="J26" s="223"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="102">
@@ -21068,7 +22960,7 @@
       <c r="D27" s="101">
         <v>44.2</v>
       </c>
-      <c r="E27" s="221"/>
+      <c r="E27" s="224"/>
       <c r="F27" s="98">
         <v>3</v>
       </c>
@@ -21082,7 +22974,7 @@
         <f>1.08*13.5</f>
         <v>14.580000000000002</v>
       </c>
-      <c r="J27" s="220"/>
+      <c r="J27" s="223"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -21106,7 +22998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -21124,29 +23016,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="217" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
     </row>
     <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="213" t="s">
+      <c r="B2" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
+      <c r="C2" s="216"/>
+      <c r="D2" s="216"/>
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
       <c r="G2" s="79" t="s">
         <v>814</v>
       </c>
@@ -21161,13 +23053,13 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="213"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="216"/>
       <c r="G3" s="90" t="s">
         <v>531</v>
       </c>
@@ -21179,17 +23071,17 @@
         <v>208.6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
       <c r="G4" s="88" t="s">
         <v>539</v>
       </c>
@@ -21201,17 +23093,17 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="79">
         <v>3</v>
       </c>
-      <c r="B5" s="213" t="s">
+      <c r="B5" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="213"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
       <c r="G5" s="90" t="s">
         <v>546</v>
       </c>
@@ -21227,13 +23119,13 @@
       <c r="A6" s="79">
         <v>4</v>
       </c>
-      <c r="B6" s="213" t="s">
+      <c r="B6" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="213"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="213"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
       <c r="G6" s="88" t="s">
         <v>553</v>
       </c>
@@ -21249,13 +23141,13 @@
       <c r="A7" s="79">
         <v>5</v>
       </c>
-      <c r="B7" s="213" t="s">
+      <c r="B7" s="216" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="213"/>
-      <c r="D7" s="213"/>
-      <c r="E7" s="213"/>
-      <c r="F7" s="213"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="216"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
       <c r="G7" s="90" t="s">
         <v>560</v>
       </c>
@@ -21268,15 +23160,15 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="218"/>
-      <c r="B8" s="218"/>
-      <c r="C8" s="218"/>
-      <c r="D8" s="218"/>
-      <c r="E8" s="218"/>
-      <c r="F8" s="218"/>
-      <c r="G8" s="218"/>
-      <c r="H8" s="218"/>
-      <c r="I8" s="218"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="221"/>
+      <c r="C8" s="221"/>
+      <c r="D8" s="221"/>
+      <c r="E8" s="221"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="221"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="221"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -21291,7 +23183,7 @@
       <c r="D9" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="E9" s="221"/>
+      <c r="E9" s="224"/>
       <c r="F9" s="79" t="s">
         <v>1055</v>
       </c>
@@ -21318,7 +23210,7 @@
       <c r="D10" s="82">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E10" s="221"/>
+      <c r="E10" s="224"/>
       <c r="F10" s="93">
         <v>3</v>
       </c>
@@ -21345,7 +23237,7 @@
       <c r="D11" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E11" s="221"/>
+      <c r="E11" s="224"/>
       <c r="F11" s="93">
         <v>3</v>
       </c>
@@ -21372,7 +23264,7 @@
       <c r="D12" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E12" s="221"/>
+      <c r="E12" s="224"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -21399,7 +23291,7 @@
       <c r="D13" s="82">
         <v>31.6</v>
       </c>
-      <c r="E13" s="221"/>
+      <c r="E13" s="224"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -21426,7 +23318,7 @@
       <c r="D14" s="95">
         <v>5.9</v>
       </c>
-      <c r="E14" s="221"/>
+      <c r="E14" s="224"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -21453,7 +23345,7 @@
       <c r="D15" s="95">
         <v>36.9</v>
       </c>
-      <c r="E15" s="221"/>
+      <c r="E15" s="224"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -21480,7 +23372,7 @@
       <c r="D16" s="95">
         <v>33.9</v>
       </c>
-      <c r="E16" s="221"/>
+      <c r="E16" s="224"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -21507,7 +23399,7 @@
       <c r="D17" s="82">
         <v>5.7</v>
       </c>
-      <c r="E17" s="221"/>
+      <c r="E17" s="224"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -21534,7 +23426,7 @@
       <c r="D18" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E18" s="221"/>
+      <c r="E18" s="224"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -21561,7 +23453,7 @@
       <c r="D19" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E19" s="221"/>
+      <c r="E19" s="224"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -21588,7 +23480,7 @@
       <c r="D20" s="82">
         <v>44.2</v>
       </c>
-      <c r="E20" s="221"/>
+      <c r="E20" s="224"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -21621,7 +23513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -21671,7 +23563,244 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" style="158" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" style="112" customWidth="1"/>
+    <col min="3" max="3" width="17" style="112" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" style="112" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="112" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" style="112" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="112" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" style="112" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="112"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="172" t="s">
+        <v>829</v>
+      </c>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+    </row>
+    <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="118" t="s">
+        <v>830</v>
+      </c>
+      <c r="B2" s="173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="156" t="s">
+        <v>814</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="117" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="140">
+        <v>1</v>
+      </c>
+      <c r="B3" s="167" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="159" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G3" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="160">
+        <f>E11</f>
+        <v>51.599999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="140">
+        <v>2</v>
+      </c>
+      <c r="B4" s="167" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="157" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="160">
+        <f>H3</f>
+        <v>51.599999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="140">
+        <v>3</v>
+      </c>
+      <c r="B5" s="167" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="157" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G5" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="160">
+        <f>H4</f>
+        <v>51.599999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+    </row>
+    <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="114" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B7" s="115" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C7" s="115" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D7" s="115" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E7" s="115" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F7" s="170"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="114">
+        <v>1</v>
+      </c>
+      <c r="B8" s="139">
+        <v>20</v>
+      </c>
+      <c r="C8" s="161" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D8" s="162">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="162">
+        <f>((0.7+(1.8*2))*0.2)*B8</f>
+        <v>17.2</v>
+      </c>
+      <c r="F8" s="170"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="114">
+        <v>2</v>
+      </c>
+      <c r="B9" s="139">
+        <v>18</v>
+      </c>
+      <c r="C9" s="161" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D9" s="162">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="162">
+        <f t="shared" ref="E9:E10" si="0">((0.7+(1.8*2))*0.2)*B9</f>
+        <v>15.48</v>
+      </c>
+      <c r="F9" s="170"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="171"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="114">
+        <v>3</v>
+      </c>
+      <c r="B10" s="139">
+        <v>22</v>
+      </c>
+      <c r="C10" s="161" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D10" s="162">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="162">
+        <f t="shared" si="0"/>
+        <v>18.919999999999998</v>
+      </c>
+      <c r="F10" s="170"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="171"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="114"/>
+      <c r="B11" s="139">
+        <f>SUM(B8:B10)</f>
+        <v>60</v>
+      </c>
+      <c r="C11" s="163"/>
+      <c r="D11" s="163" t="s">
+        <v>844</v>
+      </c>
+      <c r="E11" s="162">
+        <f>SUM(E8:E10)</f>
+        <v>51.599999999999994</v>
+      </c>
+      <c r="F11" s="170"/>
+      <c r="G11" s="171"/>
+      <c r="H11" s="171"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F7:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -21690,17 +23819,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -21708,18 +23837,18 @@
       <c r="A2" s="36" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="208" t="s">
+      <c r="B2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211" t="s">
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214" t="s">
         <v>814</v>
       </c>
-      <c r="I2" s="212"/>
+      <c r="I2" s="215"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -21731,33 +23860,33 @@
       <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="B3" s="203"/>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="206" t="s">
+      <c r="B3" s="206"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="207"/>
+      <c r="I3" s="210"/>
       <c r="J3" s="39" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="40"/>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="202"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="202"/>
-      <c r="H4" s="202"/>
-      <c r="I4" s="202"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="202"/>
+      <c r="A4" s="205"/>
+      <c r="B4" s="205"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
     </row>
     <row r="5" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="41" t="s">
@@ -22273,7 +24402,646 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="21"/>
+    <col min="2" max="2" width="55.6640625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="38" style="22" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="22" customWidth="1"/>
+    <col min="5" max="6" width="16.77734375" style="22" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>815</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>814</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>827</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="21" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>826</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="25">
+        <f>E4*0.06</f>
+        <v>39.269999999999996</v>
+      </c>
+      <c r="F2" s="25">
+        <f>F4*0.06</f>
+        <v>44.506000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
+        <v>2</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="26">
+        <f>E4*0.033</f>
+        <v>21.598500000000001</v>
+      </c>
+      <c r="F3" s="26">
+        <f>F4*0.033</f>
+        <v>24.478300000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>823</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>825</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="26">
+        <f>E6+E7</f>
+        <v>654.5</v>
+      </c>
+      <c r="F4" s="26">
+        <f>F6+F7</f>
+        <v>741.76666666666677</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>818</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>824</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="23">
+        <v>12.4</v>
+      </c>
+      <c r="F5" s="23">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="23">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>819</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="30">
+        <f>383.4</f>
+        <v>383.4</v>
+      </c>
+      <c r="F6" s="30">
+        <f>383.4/0.3*0.34</f>
+        <v>434.52000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>820</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="30">
+        <v>271.10000000000002</v>
+      </c>
+      <c r="F7" s="30">
+        <f>271.1/0.3*0.34</f>
+        <v>307.24666666666673</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="23">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>821</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="30">
+        <f>E6</f>
+        <v>383.4</v>
+      </c>
+      <c r="F8" s="30">
+        <f>F6</f>
+        <v>434.52000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="23">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>822</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="30">
+        <f>E7</f>
+        <v>271.10000000000002</v>
+      </c>
+      <c r="F9" s="30">
+        <f>F7</f>
+        <v>307.24666666666673</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A10" s="23">
+        <v>9</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>630</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="30">
+        <f>E6</f>
+        <v>383.4</v>
+      </c>
+      <c r="F10" s="30">
+        <f>F6</f>
+        <v>434.52000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A11" s="23">
+        <v>10</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>630</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="30">
+        <f>E7</f>
+        <v>271.10000000000002</v>
+      </c>
+      <c r="F11" s="30">
+        <f>F7</f>
+        <v>307.24666666666673</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="21"/>
+    <col min="2" max="2" width="55.6640625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="38" style="22" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="22" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>815</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>814</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="21" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>826</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="25">
+        <f>E4*0.06</f>
+        <v>39.269999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
+        <v>2</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="26">
+        <f>E4*0.033</f>
+        <v>21.598500000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>823</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>825</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="26">
+        <f>E6+E7</f>
+        <v>654.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>818</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>824</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="23">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="23">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>819</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="30">
+        <f>383.4</f>
+        <v>383.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>820</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="30">
+        <v>271.10000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="23">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>821</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="30">
+        <f>E6</f>
+        <v>383.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="23">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>822</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="30">
+        <f>E7</f>
+        <v>271.10000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A10" s="23">
+        <v>9</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>630</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="30">
+        <f>E6</f>
+        <v>383.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A11" s="23">
+        <v>10</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>630</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="30">
+        <f>E7</f>
+        <v>271.10000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C6:I31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="11.6640625" style="109" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="108" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D6" s="108">
+        <v>186.9</v>
+      </c>
+      <c r="E6" s="108">
+        <v>35.4</v>
+      </c>
+      <c r="G6" s="108" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H6">
+        <v>187.4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="108" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D7" s="108">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="108">
+        <v>10.8</v>
+      </c>
+      <c r="G7" s="108" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H7">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="108" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D8" s="108">
+        <v>13.8</v>
+      </c>
+      <c r="E8" s="108">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D10">
+        <v>60.3</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H10">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D12">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="E12">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H12">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="I12">
+        <v>71.900000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F21" s="109" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="24" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F24" s="109" t="s">
+        <v>976</v>
+      </c>
+      <c r="G24">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="25" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F25" s="109" t="s">
+        <v>990</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F26" s="109" t="s">
+        <v>982</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F27" s="109" t="s">
+        <v>998</v>
+      </c>
+      <c r="H27">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="28" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F28" s="109" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H28">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F29" s="109" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F30" s="109" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G30" s="110" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="31" spans="6:8" x14ac:dyDescent="0.3">
+      <c r="F31" s="109" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G31" s="111">
+        <v>5.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -22290,27 +25058,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="156" t="s">
         <v>814</v>
       </c>
@@ -22325,12 +25093,12 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1123</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="157" t="s">
         <v>1136</v>
       </c>
@@ -22346,12 +25114,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="167" t="s">
         <v>1123</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="157" t="s">
         <v>1137</v>
       </c>
@@ -22364,14 +25132,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
+      <c r="A5" s="176"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="176"/>
     </row>
     <row r="6" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="114" t="s">
@@ -22386,10 +25154,10 @@
       <c r="D6" s="115" t="s">
         <v>1128</v>
       </c>
-      <c r="E6" s="167"/>
-      <c r="F6" s="168"/>
-      <c r="G6" s="168"/>
-      <c r="H6" s="168"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="171"/>
+      <c r="G6" s="171"/>
+      <c r="H6" s="171"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="114">
@@ -22405,10 +25173,10 @@
         <f>0.63*1.73*B7</f>
         <v>21.798000000000002</v>
       </c>
-      <c r="E7" s="167"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="114">
@@ -22424,10 +25192,10 @@
         <f t="shared" ref="D8:D9" si="0">0.63*1.73*B8</f>
         <v>19.618200000000002</v>
       </c>
-      <c r="E8" s="167"/>
-      <c r="F8" s="168"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="168"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="171"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="114">
@@ -22443,10 +25211,10 @@
         <f t="shared" si="0"/>
         <v>23.977800000000002</v>
       </c>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="168"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="171"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="114"/>
@@ -22461,10 +25229,10 @@
         <f>SUM(D7:D9)</f>
         <v>65.394000000000005</v>
       </c>
-      <c r="E10" s="167"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -22480,646 +25248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="21"/>
-    <col min="2" max="2" width="55.6640625" style="22" customWidth="1"/>
-    <col min="3" max="3" width="38" style="22" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="22" customWidth="1"/>
-    <col min="5" max="6" width="16.77734375" style="22" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>815</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>813</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>814</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>827</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="21" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A2" s="23">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>816</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>826</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="25">
-        <f>E4*0.06</f>
-        <v>39.269999999999996</v>
-      </c>
-      <c r="F2" s="25">
-        <f>F4*0.06</f>
-        <v>44.506000000000007</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
-        <v>2</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>817</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="26">
-        <f>E4*0.033</f>
-        <v>21.598500000000001</v>
-      </c>
-      <c r="F3" s="26">
-        <f>F4*0.033</f>
-        <v>24.478300000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23">
-        <v>3</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>823</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>825</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="26">
-        <f>E6+E7</f>
-        <v>654.5</v>
-      </c>
-      <c r="F4" s="26">
-        <f>F6+F7</f>
-        <v>741.76666666666677</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23">
-        <v>4</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>818</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>824</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="23">
-        <v>12.4</v>
-      </c>
-      <c r="F5" s="23">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23">
-        <v>5</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>819</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="30">
-        <f>383.4</f>
-        <v>383.4</v>
-      </c>
-      <c r="F6" s="30">
-        <f>383.4/0.3*0.34</f>
-        <v>434.52000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23">
-        <v>6</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>820</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="30">
-        <v>271.10000000000002</v>
-      </c>
-      <c r="F7" s="30">
-        <f>271.1/0.3*0.34</f>
-        <v>307.24666666666673</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="23">
-        <v>7</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>821</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="30">
-        <f>E6</f>
-        <v>383.4</v>
-      </c>
-      <c r="F8" s="30">
-        <f>F6</f>
-        <v>434.52000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="23">
-        <v>8</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>822</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="30">
-        <f>E7</f>
-        <v>271.10000000000002</v>
-      </c>
-      <c r="F9" s="30">
-        <f>F7</f>
-        <v>307.24666666666673</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A10" s="23">
-        <v>9</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>630</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="30">
-        <f>E6</f>
-        <v>383.4</v>
-      </c>
-      <c r="F10" s="30">
-        <f>F6</f>
-        <v>434.52000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A11" s="23">
-        <v>10</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>630</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="30">
-        <f>E7</f>
-        <v>271.10000000000002</v>
-      </c>
-      <c r="F11" s="30">
-        <f>F7</f>
-        <v>307.24666666666673</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="21"/>
-    <col min="2" max="2" width="55.6640625" style="22" customWidth="1"/>
-    <col min="3" max="3" width="38" style="22" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="22" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>815</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>813</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>814</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="21" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A2" s="23">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>816</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>826</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="25">
-        <f>E4*0.06</f>
-        <v>39.269999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
-        <v>2</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>817</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="26">
-        <f>E4*0.033</f>
-        <v>21.598500000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23">
-        <v>3</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>823</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>825</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="26">
-        <f>E6+E7</f>
-        <v>654.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23">
-        <v>4</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>818</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>824</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="23">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23">
-        <v>5</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>819</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="30">
-        <f>383.4</f>
-        <v>383.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="62.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23">
-        <v>6</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>820</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="30">
-        <v>271.10000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="23">
-        <v>7</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>821</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="30">
-        <f>E6</f>
-        <v>383.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="23">
-        <v>8</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>822</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="30">
-        <f>E7</f>
-        <v>271.10000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.35">
-      <c r="A10" s="23">
-        <v>9</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>630</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="30">
-        <f>E6</f>
-        <v>383.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="54" x14ac:dyDescent="0.35">
-      <c r="A11" s="23">
-        <v>10</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>630</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="30">
-        <f>E7</f>
-        <v>271.10000000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C6:I31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="6" max="6" width="11.6640625" style="109" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="108" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D6" s="108">
-        <v>186.9</v>
-      </c>
-      <c r="E6" s="108">
-        <v>35.4</v>
-      </c>
-      <c r="G6" s="108" t="s">
-        <v>1064</v>
-      </c>
-      <c r="H6">
-        <v>187.4</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="108" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D7" s="108">
-        <v>2.7</v>
-      </c>
-      <c r="E7" s="108">
-        <v>10.8</v>
-      </c>
-      <c r="G7" s="108" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H7">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="108" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D8" s="108">
-        <v>13.8</v>
-      </c>
-      <c r="E8" s="108">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D10">
-        <v>60.3</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H10">
-        <v>55.1</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D12">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="E12">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H12">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="I12">
-        <v>71.900000000000006</v>
-      </c>
-    </row>
-    <row r="21" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F21" s="109" t="s">
-        <v>1070</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H21" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="24" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F24" s="109" t="s">
-        <v>976</v>
-      </c>
-      <c r="G24">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="25" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F25" s="109" t="s">
-        <v>990</v>
-      </c>
-      <c r="G25">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F26" s="109" t="s">
-        <v>982</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F27" s="109" t="s">
-        <v>998</v>
-      </c>
-      <c r="H27">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="28" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F28" s="109" t="s">
-        <v>1009</v>
-      </c>
-      <c r="H28">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F29" s="109" t="s">
-        <v>1010</v>
-      </c>
-      <c r="H29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F30" s="109" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G30" s="110" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="31" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F31" s="109" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G31" s="111">
-        <v>5.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23134,23 +25263,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
     </row>
     <row r="2" spans="1:6" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
+      <c r="C2" s="174"/>
       <c r="D2" s="153" t="s">
         <v>814</v>
       </c>
@@ -23165,10 +25294,10 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1122</v>
       </c>
-      <c r="C3" s="165"/>
+      <c r="C3" s="168"/>
       <c r="D3" s="154" t="s">
         <v>1121</v>
       </c>
@@ -23180,12 +25309,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
+      <c r="A4" s="176"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23199,7 +25328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23215,27 +25344,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="146" t="s">
         <v>814</v>
       </c>
@@ -23250,12 +25379,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1118</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="147" t="s">
         <v>1120</v>
       </c>
@@ -23270,12 +25399,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="167" t="s">
         <v>1119</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="147" t="s">
         <v>1117</v>
       </c>
@@ -23290,12 +25419,12 @@
       <c r="A5" s="140">
         <v>3</v>
       </c>
-      <c r="B5" s="164" t="s">
+      <c r="B5" s="167" t="s">
         <v>1119</v>
       </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="166"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
       <c r="F5" s="147" t="s">
         <v>1116</v>
       </c>
@@ -23307,14 +25436,14 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="173"/>
-      <c r="B6" s="173"/>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="173"/>
-      <c r="H6" s="173"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -23330,7 +25459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23345,26 +25474,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -23376,12 +25505,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1112</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="115" t="s">
         <v>1076</v>
       </c>
@@ -23393,12 +25522,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="167" t="s">
         <v>1112</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="115" t="s">
         <v>1076</v>
       </c>
@@ -23407,13 +25536,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
+      <c r="A5" s="176"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="139" t="s">
@@ -23431,8 +25560,8 @@
       <c r="E6" s="139" t="s">
         <v>1110</v>
       </c>
-      <c r="F6" s="167"/>
-      <c r="G6" s="168"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="171"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="114">
@@ -23451,8 +25580,8 @@
         <f>C7*D7-29.76</f>
         <v>6622.08</v>
       </c>
-      <c r="F7" s="167"/>
-      <c r="G7" s="168"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="171"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="114">
@@ -23471,8 +25600,8 @@
         <f t="shared" ref="E8" si="0">C8*D8</f>
         <v>127.92</v>
       </c>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="171"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D9" s="139" t="s">
@@ -23482,8 +25611,8 @@
         <f>SUM(E7:E8)</f>
         <v>6750</v>
       </c>
-      <c r="F9" s="167"/>
-      <c r="G9" s="168"/>
+      <c r="F9" s="170"/>
+      <c r="G9" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -23499,7 +25628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23514,26 +25643,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -23545,12 +25674,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1111</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -23562,12 +25691,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="167" t="s">
         <v>1111</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="115" t="s">
         <v>19</v>
       </c>
@@ -23579,12 +25708,12 @@
       <c r="A5" s="114">
         <v>3</v>
       </c>
-      <c r="B5" s="164" t="s">
+      <c r="B5" s="167" t="s">
         <v>1111</v>
       </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="166"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
       <c r="F5" s="115" t="s">
         <v>19</v>
       </c>
@@ -23605,7 +25734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23620,26 +25749,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="172" t="s">
         <v>829</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>830</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -23651,12 +25780,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="167" t="s">
         <v>1077</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="169"/>
       <c r="F3" s="115" t="s">
         <v>1076</v>
       </c>
@@ -23668,12 +25797,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="167" t="s">
         <v>1077</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="166"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
       <c r="F4" s="141" t="s">
         <v>1076</v>
       </c>
@@ -23685,12 +25814,12 @@
       <c r="A5" s="114">
         <v>3</v>
       </c>
-      <c r="B5" s="164" t="s">
+      <c r="B5" s="167" t="s">
         <v>1077</v>
       </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="166"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
       <c r="F5" s="115" t="s">
         <v>1076</v>
       </c>
@@ -23714,8 +25843,8 @@
       <c r="E6" s="139" t="s">
         <v>1110</v>
       </c>
-      <c r="F6" s="174"/>
-      <c r="G6" s="175"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="178"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="139">
@@ -23735,8 +25864,8 @@
         <f t="shared" ref="E7:E8" si="0">C7*D7</f>
         <v>24.11</v>
       </c>
-      <c r="F7" s="167"/>
-      <c r="G7" s="168"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="171"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="139">
@@ -23756,8 +25885,8 @@
         <f t="shared" si="0"/>
         <v>35.580000000000005</v>
       </c>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="171"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="139">
@@ -23777,8 +25906,8 @@
         <f>C9*D9-10.8</f>
         <v>56.480000000000004</v>
       </c>
-      <c r="F9" s="167"/>
-      <c r="G9" s="168"/>
+      <c r="F9" s="170"/>
+      <c r="G9" s="171"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="139">
@@ -23798,8 +25927,8 @@
         <f>C10*D10</f>
         <v>54.33</v>
       </c>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="171"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="139">
@@ -23819,8 +25948,8 @@
         <f t="shared" ref="E11:E25" si="1">C11*D11</f>
         <v>21.8</v>
       </c>
-      <c r="F11" s="167"/>
-      <c r="G11" s="168"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="171"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="139">
@@ -23840,8 +25969,8 @@
         <f t="shared" si="1"/>
         <v>243.55</v>
       </c>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="171"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="139">
@@ -23861,8 +25990,8 @@
         <f t="shared" si="1"/>
         <v>97.42</v>
       </c>
-      <c r="F13" s="167"/>
-      <c r="G13" s="168"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="171"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="139">
@@ -23882,8 +26011,8 @@
         <f t="shared" si="1"/>
         <v>55.730000000000004</v>
       </c>
-      <c r="F14" s="167"/>
-      <c r="G14" s="168"/>
+      <c r="F14" s="170"/>
+      <c r="G14" s="171"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="139"/>
@@ -23896,8 +26025,8 @@
         <f>SUM(E7:E14)</f>
         <v>589</v>
       </c>
-      <c r="F15" s="167"/>
-      <c r="G15" s="168"/>
+      <c r="F15" s="170"/>
+      <c r="G15" s="171"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="139">
@@ -23917,8 +26046,8 @@
         <f t="shared" si="1"/>
         <v>15.149999999999999</v>
       </c>
-      <c r="F16" s="167"/>
-      <c r="G16" s="168"/>
+      <c r="F16" s="170"/>
+      <c r="G16" s="171"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="139">
@@ -23938,8 +26067,8 @@
         <f t="shared" si="1"/>
         <v>39.18</v>
       </c>
-      <c r="F17" s="167"/>
-      <c r="G17" s="168"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="171"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="139">
@@ -23959,8 +26088,8 @@
         <f t="shared" si="1"/>
         <v>21.35</v>
       </c>
-      <c r="F18" s="167"/>
-      <c r="G18" s="168"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="171"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="139">
@@ -23980,8 +26109,8 @@
         <f t="shared" si="1"/>
         <v>23.419999999999998</v>
       </c>
-      <c r="F19" s="167"/>
-      <c r="G19" s="168"/>
+      <c r="F19" s="170"/>
+      <c r="G19" s="171"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="139">
@@ -24001,8 +26130,8 @@
         <f t="shared" si="1"/>
         <v>21.349999999999998</v>
       </c>
-      <c r="F20" s="167"/>
-      <c r="G20" s="168"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="171"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="139">
@@ -24022,8 +26151,8 @@
         <f>C21*D21-13.44</f>
         <v>108.67999999999999</v>
       </c>
-      <c r="F21" s="167"/>
-      <c r="G21" s="168"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="171"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="139">
@@ -24043,8 +26172,8 @@
         <f t="shared" si="1"/>
         <v>30.529999999999998</v>
       </c>
-      <c r="F22" s="167"/>
-      <c r="G22" s="168"/>
+      <c r="F22" s="170"/>
+      <c r="G22" s="171"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="139">
@@ -24064,8 +26193,8 @@
         <f t="shared" si="1"/>
         <v>27.089999999999996</v>
       </c>
-      <c r="F23" s="167"/>
-      <c r="G23" s="168"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="171"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="139">
@@ -24085,8 +26214,8 @@
         <f t="shared" si="1"/>
         <v>57.79</v>
       </c>
-      <c r="F24" s="167"/>
-      <c r="G24" s="168"/>
+      <c r="F24" s="170"/>
+      <c r="G24" s="171"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="139">
@@ -24106,8 +26235,8 @@
         <f t="shared" si="1"/>
         <v>28.46</v>
       </c>
-      <c r="F25" s="167"/>
-      <c r="G25" s="168"/>
+      <c r="F25" s="170"/>
+      <c r="G25" s="171"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="139"/>
@@ -24120,8 +26249,8 @@
         <f>SUM(E16:E25)</f>
         <v>372.99999999999994</v>
       </c>
-      <c r="F26" s="167"/>
-      <c r="G26" s="168"/>
+      <c r="F26" s="170"/>
+      <c r="G26" s="171"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="139">
@@ -24141,8 +26270,8 @@
         <f t="shared" ref="E27:E36" si="2">C27*D27</f>
         <v>33.06</v>
       </c>
-      <c r="F27" s="167"/>
-      <c r="G27" s="168"/>
+      <c r="F27" s="170"/>
+      <c r="G27" s="171"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="139">
@@ -24162,8 +26291,8 @@
         <f>C28*D28-7.92</f>
         <v>31.259999999999998</v>
       </c>
-      <c r="F28" s="167"/>
-      <c r="G28" s="168"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="171"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="139">
@@ -24183,8 +26312,8 @@
         <f t="shared" si="2"/>
         <v>19.97</v>
       </c>
-      <c r="F29" s="167"/>
-      <c r="G29" s="168"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="171"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="139">
@@ -24204,8 +26333,8 @@
         <f t="shared" si="2"/>
         <v>21.44</v>
       </c>
-      <c r="F30" s="167"/>
-      <c r="G30" s="168"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="171"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="139">
@@ -24225,8 +26354,8 @@
         <f t="shared" si="2"/>
         <v>21.349999999999998</v>
       </c>
-      <c r="F31" s="167"/>
-      <c r="G31" s="168"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="171"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="139">
@@ -24246,8 +26375,8 @@
         <f t="shared" si="2"/>
         <v>183.17999999999998</v>
       </c>
-      <c r="F32" s="167"/>
-      <c r="G32" s="168"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="171"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="139">
@@ -24267,8 +26396,8 @@
         <f t="shared" si="2"/>
         <v>30.56</v>
       </c>
-      <c r="F33" s="167"/>
-      <c r="G33" s="168"/>
+      <c r="F33" s="170"/>
+      <c r="G33" s="171"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="139">
@@ -24288,8 +26417,8 @@
         <f t="shared" si="2"/>
         <v>27.089999999999996</v>
       </c>
-      <c r="F34" s="167"/>
-      <c r="G34" s="168"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="171"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="139">
@@ -24309,8 +26438,8 @@
         <f t="shared" si="2"/>
         <v>28.46</v>
       </c>
-      <c r="F35" s="167"/>
-      <c r="G35" s="168"/>
+      <c r="F35" s="170"/>
+      <c r="G35" s="171"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="139">
@@ -24330,8 +26459,8 @@
         <f t="shared" si="2"/>
         <v>29.839999999999996</v>
       </c>
-      <c r="F36" s="167"/>
-      <c r="G36" s="168"/>
+      <c r="F36" s="170"/>
+      <c r="G36" s="171"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="139">
@@ -24351,8 +26480,8 @@
         <f>C37*D37</f>
         <v>57.79</v>
       </c>
-      <c r="F37" s="167"/>
-      <c r="G37" s="168"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="171"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="139"/>
@@ -24365,8 +26494,8 @@
         <f>SUM(E27:E37)</f>
         <v>483.99999999999994</v>
       </c>
-      <c r="F38" s="167"/>
-      <c r="G38" s="168"/>
+      <c r="F38" s="170"/>
+      <c r="G38" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -24382,7 +26511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -24425,43 +26554,43 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="180" t="s">
+      <c r="A3" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="180"/>
-      <c r="C3" s="180"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="180"/>
-      <c r="H3" s="180"/>
-      <c r="I3" s="180"/>
+      <c r="B3" s="183"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="181" t="s">
+      <c r="A4" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="181"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="181"/>
-      <c r="G4" s="181"/>
-      <c r="H4" s="181"/>
-      <c r="I4" s="181"/>
+      <c r="B4" s="184"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
     </row>
     <row r="5" spans="1:11" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
@@ -35682,15 +37811,15 @@
       <c r="B501" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="C501" s="176" t="s">
+      <c r="C501" s="179" t="s">
         <v>778</v>
       </c>
-      <c r="D501" s="177"/>
-      <c r="E501" s="177"/>
-      <c r="F501" s="177"/>
-      <c r="G501" s="177"/>
-      <c r="H501" s="177"/>
-      <c r="I501" s="178"/>
+      <c r="D501" s="180"/>
+      <c r="E501" s="180"/>
+      <c r="F501" s="180"/>
+      <c r="G501" s="180"/>
+      <c r="H501" s="180"/>
+      <c r="I501" s="181"/>
     </row>
     <row r="502" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
@@ -35726,15 +37855,15 @@
       <c r="B503" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C503" s="176" t="s">
+      <c r="C503" s="179" t="s">
         <v>787</v>
       </c>
-      <c r="D503" s="177"/>
-      <c r="E503" s="177"/>
-      <c r="F503" s="177"/>
-      <c r="G503" s="177"/>
-      <c r="H503" s="177"/>
-      <c r="I503" s="178"/>
+      <c r="D503" s="180"/>
+      <c r="E503" s="180"/>
+      <c r="F503" s="180"/>
+      <c r="G503" s="180"/>
+      <c r="H503" s="180"/>
+      <c r="I503" s="181"/>
     </row>
     <row r="504" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
@@ -35743,15 +37872,15 @@
       <c r="B504" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="C504" s="176" t="s">
+      <c r="C504" s="179" t="s">
         <v>790</v>
       </c>
-      <c r="D504" s="177"/>
-      <c r="E504" s="177"/>
-      <c r="F504" s="177"/>
-      <c r="G504" s="177"/>
-      <c r="H504" s="177"/>
-      <c r="I504" s="178"/>
+      <c r="D504" s="180"/>
+      <c r="E504" s="180"/>
+      <c r="F504" s="180"/>
+      <c r="G504" s="180"/>
+      <c r="H504" s="180"/>
+      <c r="I504" s="181"/>
     </row>
     <row r="505" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
@@ -35787,15 +37916,15 @@
       <c r="B506" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="C506" s="176" t="s">
+      <c r="C506" s="179" t="s">
         <v>798</v>
       </c>
-      <c r="D506" s="177"/>
-      <c r="E506" s="177"/>
-      <c r="F506" s="177"/>
-      <c r="G506" s="177"/>
-      <c r="H506" s="177"/>
-      <c r="I506" s="178"/>
+      <c r="D506" s="180"/>
+      <c r="E506" s="180"/>
+      <c r="F506" s="180"/>
+      <c r="G506" s="180"/>
+      <c r="H506" s="180"/>
+      <c r="I506" s="181"/>
     </row>
     <row r="507" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
@@ -35804,15 +37933,15 @@
       <c r="B507" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="C507" s="176" t="s">
+      <c r="C507" s="179" t="s">
         <v>801</v>
       </c>
-      <c r="D507" s="177"/>
-      <c r="E507" s="177"/>
-      <c r="F507" s="177"/>
-      <c r="G507" s="177"/>
-      <c r="H507" s="177"/>
-      <c r="I507" s="178"/>
+      <c r="D507" s="180"/>
+      <c r="E507" s="180"/>
+      <c r="F507" s="180"/>
+      <c r="G507" s="180"/>
+      <c r="H507" s="180"/>
+      <c r="I507" s="181"/>
     </row>
     <row r="508" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
@@ -35821,15 +37950,15 @@
       <c r="B508" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="C508" s="176" t="s">
+      <c r="C508" s="179" t="s">
         <v>778</v>
       </c>
-      <c r="D508" s="177"/>
-      <c r="E508" s="177"/>
-      <c r="F508" s="177"/>
-      <c r="G508" s="177"/>
-      <c r="H508" s="177"/>
-      <c r="I508" s="178"/>
+      <c r="D508" s="180"/>
+      <c r="E508" s="180"/>
+      <c r="F508" s="180"/>
+      <c r="G508" s="180"/>
+      <c r="H508" s="180"/>
+      <c r="I508" s="181"/>
     </row>
     <row r="509" spans="1:9" ht="90" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
@@ -35899,1104 +38028,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P31"/>
-  <sheetFormatPr defaultRowHeight="23.4" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="2" max="2" width="52.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="10" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" customWidth="1"/>
-    <col min="9" max="9" width="38" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
-        <v>905</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>906</v>
-      </c>
-      <c r="C1" s="68" t="s">
-        <v>907</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>908</v>
-      </c>
-      <c r="E1" s="64" t="s">
-        <v>909</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>910</v>
-      </c>
-      <c r="G1" s="70" t="s">
-        <v>911</v>
-      </c>
-      <c r="N1" s="44" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="71" t="s">
-        <v>942</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="66">
-        <v>5092.3999999999996</v>
-      </c>
-      <c r="F2" s="66">
-        <v>4104.6000000000004</v>
-      </c>
-      <c r="G2" s="66">
-        <f>E2+F2</f>
-        <v>9197</v>
-      </c>
-      <c r="I2" s="61" t="s">
-        <v>358</v>
-      </c>
-      <c r="J2" s="62">
-        <v>9197</v>
-      </c>
-      <c r="L2" s="72">
-        <f>G2-J2</f>
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>9779.2999999999993</v>
-      </c>
-      <c r="P2" s="78">
-        <f t="shared" ref="P2:P29" si="0">J2-N2</f>
-        <v>-582.29999999999927</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="63" t="s">
-        <v>885</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>912</v>
-      </c>
-      <c r="C3" s="66">
-        <v>0</v>
-      </c>
-      <c r="D3" s="66">
-        <v>0</v>
-      </c>
-      <c r="E3" s="66">
-        <v>7</v>
-      </c>
-      <c r="F3" s="66">
-        <v>7</v>
-      </c>
-      <c r="G3" s="66">
-        <f>E3+F3</f>
-        <v>14</v>
-      </c>
-      <c r="I3" s="59" t="s">
-        <v>363</v>
-      </c>
-      <c r="J3" s="60">
-        <v>14</v>
-      </c>
-      <c r="L3" s="72">
-        <f t="shared" ref="L3:L31" si="1">G3-J3</f>
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>8.4</v>
-      </c>
-      <c r="P3" s="78">
-        <f t="shared" si="0"/>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
-        <v>886</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>913</v>
-      </c>
-      <c r="C4" s="66">
-        <v>0</v>
-      </c>
-      <c r="D4" s="66">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="E4" s="66">
-        <v>18.7</v>
-      </c>
-      <c r="F4" s="66">
-        <v>30.7</v>
-      </c>
-      <c r="G4" s="66">
-        <f t="shared" ref="G4:G31" si="2">E4+F4</f>
-        <v>49.4</v>
-      </c>
-      <c r="I4" s="61" t="s">
-        <v>368</v>
-      </c>
-      <c r="J4" s="62">
-        <v>49.4</v>
-      </c>
-      <c r="L4" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>55.3</v>
-      </c>
-      <c r="P4" s="78">
-        <f t="shared" si="0"/>
-        <v>-5.8999999999999986</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
-        <v>887</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>914</v>
-      </c>
-      <c r="C5" s="66">
-        <v>0</v>
-      </c>
-      <c r="D5" s="66">
-        <v>0</v>
-      </c>
-      <c r="E5" s="66">
-        <v>8.4</v>
-      </c>
-      <c r="F5" s="66">
-        <v>24.4</v>
-      </c>
-      <c r="G5" s="66">
-        <f t="shared" si="2"/>
-        <v>32.799999999999997</v>
-      </c>
-      <c r="I5" s="59" t="s">
-        <v>373</v>
-      </c>
-      <c r="J5" s="60">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="L5" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="P5" s="78">
-        <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="63" t="s">
-        <v>888</v>
-      </c>
-      <c r="B6" s="64" t="s">
-        <v>915</v>
-      </c>
-      <c r="C6" s="66">
-        <v>0</v>
-      </c>
-      <c r="D6" s="66">
-        <v>0</v>
-      </c>
-      <c r="E6" s="66">
-        <v>4</v>
-      </c>
-      <c r="F6" s="66">
-        <v>3.9</v>
-      </c>
-      <c r="G6" s="66">
-        <f t="shared" si="2"/>
-        <v>7.9</v>
-      </c>
-      <c r="I6" s="61" t="s">
-        <v>378</v>
-      </c>
-      <c r="J6" s="62">
-        <v>7.9</v>
-      </c>
-      <c r="L6" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>10.1</v>
-      </c>
-      <c r="P6" s="78">
-        <f t="shared" si="0"/>
-        <v>-2.1999999999999993</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="63" t="s">
-        <v>889</v>
-      </c>
-      <c r="B7" s="64" t="s">
-        <v>916</v>
-      </c>
-      <c r="C7" s="66">
-        <v>0</v>
-      </c>
-      <c r="D7" s="66">
-        <v>9.6</v>
-      </c>
-      <c r="E7" s="66">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="F7" s="66">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G7" s="66">
-        <f t="shared" si="2"/>
-        <v>18.100000000000001</v>
-      </c>
-      <c r="I7" s="59" t="s">
-        <v>383</v>
-      </c>
-      <c r="J7" s="60">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="L7" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>23.4</v>
-      </c>
-      <c r="P7" s="78">
-        <f t="shared" si="0"/>
-        <v>-5.2999999999999972</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="63" t="s">
-        <v>890</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>917</v>
-      </c>
-      <c r="C8" s="66">
-        <v>0</v>
-      </c>
-      <c r="D8" s="66">
-        <v>16.7</v>
-      </c>
-      <c r="E8" s="66">
-        <v>15.9</v>
-      </c>
-      <c r="F8" s="66">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="G8" s="66">
-        <f t="shared" si="2"/>
-        <v>32.799999999999997</v>
-      </c>
-      <c r="I8" s="61" t="s">
-        <v>388</v>
-      </c>
-      <c r="J8" s="62">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="L8" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>43.7</v>
-      </c>
-      <c r="P8" s="78">
-        <f t="shared" si="0"/>
-        <v>-10.900000000000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="62"/>
-      <c r="L9" s="72"/>
-      <c r="N9">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="P9" s="78">
-        <f t="shared" si="0"/>
-        <v>-78.400000000000006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="62"/>
-      <c r="L10" s="72"/>
-      <c r="N10">
-        <v>742.1</v>
-      </c>
-      <c r="P10" s="78">
-        <f t="shared" si="0"/>
-        <v>-742.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="63" t="s">
-        <v>918</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>919</v>
-      </c>
-      <c r="C11" s="66">
-        <v>0</v>
-      </c>
-      <c r="D11" s="66">
-        <v>0</v>
-      </c>
-      <c r="E11" s="66">
-        <v>2.8</v>
-      </c>
-      <c r="F11" s="66">
-        <v>2.8</v>
-      </c>
-      <c r="G11" s="66">
-        <f t="shared" si="2"/>
-        <v>5.6</v>
-      </c>
-      <c r="I11" s="59" t="s">
-        <v>393</v>
-      </c>
-      <c r="J11" s="60">
-        <v>5.6</v>
-      </c>
-      <c r="L11" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="78">
-        <f t="shared" si="0"/>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63" t="s">
-        <v>920</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>921</v>
-      </c>
-      <c r="C12" s="66">
-        <v>0</v>
-      </c>
-      <c r="D12" s="66">
-        <v>229.6</v>
-      </c>
-      <c r="E12" s="66">
-        <v>355.8</v>
-      </c>
-      <c r="F12" s="66">
-        <v>388.9</v>
-      </c>
-      <c r="G12" s="66">
-        <f t="shared" si="2"/>
-        <v>744.7</v>
-      </c>
-      <c r="I12" s="61" t="s">
-        <v>398</v>
-      </c>
-      <c r="J12" s="62">
-        <v>744.7</v>
-      </c>
-      <c r="L12" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="78">
-        <f t="shared" si="0"/>
-        <v>744.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="63" t="s">
-        <v>891</v>
-      </c>
-      <c r="B13" s="64" t="s">
-        <v>922</v>
-      </c>
-      <c r="C13" s="66">
-        <v>1208</v>
-      </c>
-      <c r="D13" s="66">
-        <v>2697.6</v>
-      </c>
-      <c r="E13" s="66">
-        <v>1957.3</v>
-      </c>
-      <c r="F13" s="66">
-        <v>1990.5</v>
-      </c>
-      <c r="G13" s="66">
-        <f t="shared" si="2"/>
-        <v>3947.8</v>
-      </c>
-      <c r="I13" s="59" t="s">
-        <v>403</v>
-      </c>
-      <c r="J13" s="60">
-        <v>3947.8</v>
-      </c>
-      <c r="L13" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>4000.3</v>
-      </c>
-      <c r="P13" s="78">
-        <f t="shared" si="0"/>
-        <v>-52.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="63" t="s">
-        <v>923</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>924</v>
-      </c>
-      <c r="C14" s="66">
-        <v>0</v>
-      </c>
-      <c r="D14" s="66">
-        <v>6.8</v>
-      </c>
-      <c r="E14" s="66">
-        <v>0</v>
-      </c>
-      <c r="F14" s="66">
-        <v>0</v>
-      </c>
-      <c r="G14" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="78">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="63" t="s">
-        <v>925</v>
-      </c>
-      <c r="B15" s="64" t="s">
-        <v>926</v>
-      </c>
-      <c r="C15" s="66">
-        <v>0</v>
-      </c>
-      <c r="D15" s="66">
-        <v>89.4</v>
-      </c>
-      <c r="E15" s="66">
-        <v>94.4</v>
-      </c>
-      <c r="F15" s="66">
-        <v>0</v>
-      </c>
-      <c r="G15" s="66">
-        <f t="shared" si="2"/>
-        <v>94.4</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>408</v>
-      </c>
-      <c r="J15" s="62">
-        <v>94.4</v>
-      </c>
-      <c r="L15" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="78">
-        <f t="shared" si="0"/>
-        <v>94.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="63" t="s">
-        <v>892</v>
-      </c>
-      <c r="B16" s="64" t="s">
-        <v>927</v>
-      </c>
-      <c r="C16" s="66">
-        <v>0</v>
-      </c>
-      <c r="D16" s="66">
-        <v>21.1</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0</v>
-      </c>
-      <c r="G16" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="72"/>
-      <c r="P16" s="78"/>
-    </row>
-    <row r="17" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="63" t="s">
-        <v>893</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>928</v>
-      </c>
-      <c r="C17" s="66">
-        <v>0</v>
-      </c>
-      <c r="D17" s="66">
-        <v>0</v>
-      </c>
-      <c r="E17" s="66">
-        <v>0</v>
-      </c>
-      <c r="F17" s="66">
-        <v>24.9</v>
-      </c>
-      <c r="G17" s="66">
-        <f t="shared" si="2"/>
-        <v>24.9</v>
-      </c>
-      <c r="I17" s="59" t="s">
-        <v>413</v>
-      </c>
-      <c r="J17" s="60">
-        <v>24.9</v>
-      </c>
-      <c r="L17" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>23.2</v>
-      </c>
-      <c r="P17" s="78">
-        <f t="shared" si="0"/>
-        <v>1.6999999999999993</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="63" t="s">
-        <v>894</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>929</v>
-      </c>
-      <c r="C18" s="66">
-        <v>0</v>
-      </c>
-      <c r="D18" s="66">
-        <v>671.4</v>
-      </c>
-      <c r="E18" s="66">
-        <v>458.6</v>
-      </c>
-      <c r="F18" s="66">
-        <v>191.2</v>
-      </c>
-      <c r="G18" s="66">
-        <f t="shared" si="2"/>
-        <v>649.79999999999995</v>
-      </c>
-      <c r="I18" s="61" t="s">
-        <v>418</v>
-      </c>
-      <c r="J18" s="62">
-        <v>649.79999999999995</v>
-      </c>
-      <c r="L18" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>239.5</v>
-      </c>
-      <c r="P18" s="78">
-        <f t="shared" si="0"/>
-        <v>410.29999999999995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="63" t="s">
-        <v>895</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>930</v>
-      </c>
-      <c r="C19" s="66">
-        <v>0</v>
-      </c>
-      <c r="D19" s="66">
-        <v>22</v>
-      </c>
-      <c r="E19" s="66">
-        <v>0</v>
-      </c>
-      <c r="F19" s="66">
-        <v>0</v>
-      </c>
-      <c r="G19" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="72"/>
-      <c r="P19" s="78"/>
-    </row>
-    <row r="20" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="63" t="s">
-        <v>896</v>
-      </c>
-      <c r="B20" s="64" t="s">
-        <v>931</v>
-      </c>
-      <c r="C20" s="65">
-        <v>0</v>
-      </c>
-      <c r="D20" s="65">
-        <v>382.5</v>
-      </c>
-      <c r="E20" s="65">
-        <v>201.8</v>
-      </c>
-      <c r="F20" s="65">
-        <v>152</v>
-      </c>
-      <c r="G20" s="66">
-        <f t="shared" si="2"/>
-        <v>353.8</v>
-      </c>
-      <c r="I20" s="59" t="s">
-        <v>531</v>
-      </c>
-      <c r="J20" s="60">
-        <v>353.8</v>
-      </c>
-      <c r="L20" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>365.8</v>
-      </c>
-      <c r="P20" s="78">
-        <f t="shared" si="0"/>
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="63" t="s">
-        <v>897</v>
-      </c>
-      <c r="B21" s="64" t="s">
-        <v>932</v>
-      </c>
-      <c r="C21" s="65">
-        <v>0</v>
-      </c>
-      <c r="D21" s="65">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="E21" s="65">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="F21" s="65">
-        <v>21</v>
-      </c>
-      <c r="G21" s="66">
-        <f t="shared" si="2"/>
-        <v>59.7</v>
-      </c>
-      <c r="I21" s="61" t="s">
-        <v>539</v>
-      </c>
-      <c r="J21" s="62">
-        <v>59.7</v>
-      </c>
-      <c r="L21" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>48.3</v>
-      </c>
-      <c r="P21" s="78">
-        <f t="shared" si="0"/>
-        <v>11.400000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63" t="s">
-        <v>898</v>
-      </c>
-      <c r="B22" s="64" t="s">
-        <v>933</v>
-      </c>
-      <c r="C22" s="65">
-        <v>0</v>
-      </c>
-      <c r="D22" s="65">
-        <v>86.2</v>
-      </c>
-      <c r="E22" s="65">
-        <v>64</v>
-      </c>
-      <c r="F22" s="65">
-        <v>43.8</v>
-      </c>
-      <c r="G22" s="66">
-        <f t="shared" si="2"/>
-        <v>107.8</v>
-      </c>
-      <c r="I22" s="59" t="s">
-        <v>546</v>
-      </c>
-      <c r="J22" s="60">
-        <v>107.8</v>
-      </c>
-      <c r="L22" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>91.8</v>
-      </c>
-      <c r="P22" s="78">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="71" t="s">
-        <v>884</v>
-      </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="77"/>
-      <c r="L23" s="72"/>
-      <c r="N23">
-        <v>11.5</v>
-      </c>
-      <c r="P23" s="78">
-        <f t="shared" si="0"/>
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="71" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="66"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="77"/>
-      <c r="L24" s="72"/>
-      <c r="N24">
-        <v>16.3</v>
-      </c>
-      <c r="P24" s="78">
-        <f t="shared" si="0"/>
-        <v>-16.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="63" t="s">
-        <v>899</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>934</v>
-      </c>
-      <c r="C25" s="66">
-        <v>0</v>
-      </c>
-      <c r="D25" s="66">
-        <v>169.5</v>
-      </c>
-      <c r="E25" s="66">
-        <v>0</v>
-      </c>
-      <c r="F25" s="66">
-        <v>0</v>
-      </c>
-      <c r="G25" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="72"/>
-      <c r="P25" s="78"/>
-    </row>
-    <row r="26" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="63" t="s">
-        <v>900</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>935</v>
-      </c>
-      <c r="C26" s="65">
-        <v>0</v>
-      </c>
-      <c r="D26" s="65">
-        <v>1784.9</v>
-      </c>
-      <c r="E26" s="65">
-        <v>171.1</v>
-      </c>
-      <c r="F26" s="65">
-        <v>125.1</v>
-      </c>
-      <c r="G26" s="66">
-        <f t="shared" si="2"/>
-        <v>296.2</v>
-      </c>
-      <c r="I26" s="61" t="s">
-        <v>553</v>
-      </c>
-      <c r="J26" s="62">
-        <v>296.2</v>
-      </c>
-      <c r="L26" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>302.8</v>
-      </c>
-      <c r="P26" s="78">
-        <f t="shared" si="0"/>
-        <v>-6.6000000000000227</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="63" t="s">
-        <v>901</v>
-      </c>
-      <c r="B27" s="64" t="s">
-        <v>936</v>
-      </c>
-      <c r="C27" s="65">
-        <v>0</v>
-      </c>
-      <c r="D27" s="65">
-        <v>204.1</v>
-      </c>
-      <c r="E27" s="65">
-        <v>0</v>
-      </c>
-      <c r="F27" s="65">
-        <v>0</v>
-      </c>
-      <c r="G27" s="66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="78">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="63" t="s">
-        <v>902</v>
-      </c>
-      <c r="B28" s="64" t="s">
-        <v>937</v>
-      </c>
-      <c r="C28" s="65">
-        <v>0</v>
-      </c>
-      <c r="D28" s="65">
-        <v>397.1</v>
-      </c>
-      <c r="E28" s="65">
-        <v>400.4</v>
-      </c>
-      <c r="F28" s="65">
-        <v>351.3</v>
-      </c>
-      <c r="G28" s="66">
-        <f t="shared" si="2"/>
-        <v>751.7</v>
-      </c>
-      <c r="I28" s="59" t="s">
-        <v>560</v>
-      </c>
-      <c r="J28" s="60">
-        <v>751.7</v>
-      </c>
-      <c r="L28" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>751.5</v>
-      </c>
-      <c r="P28" s="78">
-        <f t="shared" si="0"/>
-        <v>0.20000000000004547</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="63" t="s">
-        <v>903</v>
-      </c>
-      <c r="B29" s="64" t="s">
-        <v>938</v>
-      </c>
-      <c r="C29" s="66">
-        <v>0</v>
-      </c>
-      <c r="D29" s="66">
-        <v>24</v>
-      </c>
-      <c r="E29" s="66">
-        <v>11.6</v>
-      </c>
-      <c r="F29" s="66">
-        <v>12.8</v>
-      </c>
-      <c r="G29" s="66">
-        <f t="shared" si="2"/>
-        <v>24.4</v>
-      </c>
-      <c r="L29" s="72">
-        <f t="shared" si="1"/>
-        <v>24.4</v>
-      </c>
-      <c r="N29">
-        <v>24.5</v>
-      </c>
-      <c r="P29" s="78">
-        <f t="shared" si="0"/>
-        <v>-24.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="63" t="s">
-        <v>904</v>
-      </c>
-      <c r="B30" s="64" t="s">
-        <v>939</v>
-      </c>
-      <c r="C30" s="65">
-        <v>0</v>
-      </c>
-      <c r="D30" s="65">
-        <v>4.3</v>
-      </c>
-      <c r="E30" s="65">
-        <v>3.9</v>
-      </c>
-      <c r="F30" s="65">
-        <v>3.9</v>
-      </c>
-      <c r="G30" s="66">
-        <f t="shared" si="2"/>
-        <v>7.8</v>
-      </c>
-      <c r="I30" s="61" t="s">
-        <v>567</v>
-      </c>
-      <c r="J30" s="62">
-        <v>7.8</v>
-      </c>
-      <c r="L30" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="P30" s="78">
-        <f>J30-N30</f>
-        <v>-0.50000000000000089</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="63" t="s">
-        <v>940</v>
-      </c>
-      <c r="B31" s="64" t="s">
-        <v>941</v>
-      </c>
-      <c r="C31" s="66">
-        <v>0</v>
-      </c>
-      <c r="D31" s="66">
-        <v>0</v>
-      </c>
-      <c r="E31" s="66">
-        <v>0</v>
-      </c>
-      <c r="F31" s="66">
-        <v>3.8</v>
-      </c>
-      <c r="G31" s="66">
-        <f t="shared" si="2"/>
-        <v>3.8</v>
-      </c>
-      <c r="L31" s="72">
-        <f t="shared" si="1"/>
-        <v>3.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/school_2/1) walls/walls_sh2.xlsx
+++ b/school_2/1) walls/walls_sh2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="6" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="10.3отк" sheetId="30" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="1228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3371" uniqueCount="1225">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -11981,27 +11981,9 @@
     <t xml:space="preserve">Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой </t>
   </si>
   <si>
-    <t>Подготовка поверхности СКБ /  Шпатлёвка базовая</t>
-  </si>
-  <si>
-    <t>Подготовка поверхности СКБ /  Шпатлёвка финнишная</t>
-  </si>
-  <si>
     <t>СТ-2.3</t>
   </si>
   <si>
-    <t>Лакокрасочные работы СКБ / 2 слоя / СТ-2.16</t>
-  </si>
-  <si>
-    <t>Лакокрасочные работы СКБ / 2 слоя / СТ-2.1</t>
-  </si>
-  <si>
-    <t>Лакокрасочные работы СКБ / 2 слоя / СТ-1.1</t>
-  </si>
-  <si>
-    <t>Лакокрасочные работы СКБ / 2 слоя / СТ-2.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Подготовка поверхности СКБ </t>
   </si>
   <si>
@@ -12029,18 +12011,6 @@
     <t>окна высокие</t>
   </si>
   <si>
-    <t>окна высокие, h=6.800</t>
-  </si>
-  <si>
-    <t>окна h=2.500</t>
-  </si>
-  <si>
-    <t>витражи h=3.800</t>
-  </si>
-  <si>
-    <t>двери h=2.100</t>
-  </si>
-  <si>
     <t>Кол-во откосов, шт</t>
   </si>
   <si>
@@ -12066,6 +12036,27 @@
   </si>
   <si>
     <t>Лакокрасочные работы СКБ / окраска откосов / в 2 слоя</t>
+  </si>
+  <si>
+    <t>Штукатурка поверхностей откосов сухими смесями с предварительной огрунтовкой поверхности</t>
+  </si>
+  <si>
+    <t>Выравнивание поверхностей откосов толщ. до 5 мм с предварительной огрунтовкой поверхности (базовая шпаклевка)</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска откосов / 2 слоя / СТ-2.1</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска откосов  / 2 слоя / СТ-2.16</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска откосов  / 2 слоя / СТ-1.1</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска откосов  / 2 слоя / СТ-2.3</t>
+  </si>
+  <si>
+    <t>Выравнивание поверхностей откосов толщ. до 5 мм с предварительной огрунтовкой поверхности (финишная шпаклевка)</t>
   </si>
 </sst>
 </file>
@@ -13223,24 +13214,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -13263,6 +13236,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13364,21 +13355,6 @@
     <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13396,6 +13372,21 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13433,6 +13424,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13452,9 +13446,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14856,7 +14847,7 @@
       <c r="C3" s="200"/>
       <c r="D3" s="200"/>
       <c r="E3" s="205" t="s">
-        <v>1224</v>
+        <v>1214</v>
       </c>
       <c r="F3" s="206"/>
       <c r="G3" s="115" t="s">
@@ -14871,7 +14862,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="200" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C4" s="200"/>
       <c r="D4" s="200"/>
@@ -14892,7 +14883,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="200" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="C5" s="200"/>
       <c r="D5" s="200"/>
@@ -14920,7 +14911,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="196" t="s">
-        <v>1219</v>
+        <v>1209</v>
       </c>
       <c r="B7" s="196"/>
       <c r="C7" s="196"/>
@@ -14932,19 +14923,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="190" t="s">
-        <v>1222</v>
+        <v>1212</v>
       </c>
       <c r="B8" s="190" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C8" s="190" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="D8" s="190" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="E8" s="190" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="F8" s="194"/>
       <c r="G8" s="195"/>
@@ -14952,7 +14943,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="190" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="B9" s="190">
         <v>70</v>
@@ -14968,7 +14959,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="190" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B10" s="190">
         <v>52</v>
@@ -14988,7 +14979,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="190" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B11" s="190">
         <v>37</v>
@@ -15006,7 +14997,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="197" t="s">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="B12" s="197"/>
       <c r="C12" s="197"/>
@@ -15018,19 +15009,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="191" t="s">
-        <v>1222</v>
+        <v>1212</v>
       </c>
       <c r="B13" s="191" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C13" s="191" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="D13" s="191" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="E13" s="191" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="F13" s="194"/>
       <c r="G13" s="195"/>
@@ -15038,7 +15029,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="191" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="B14" s="191">
         <v>17.649999999999999</v>
@@ -15054,7 +15045,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="191" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B15" s="191">
         <v>12.2</v>
@@ -15074,7 +15065,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="191" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B16" s="191">
         <v>6.9</v>
@@ -15092,7 +15083,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="198" t="s">
-        <v>1221</v>
+        <v>1211</v>
       </c>
       <c r="B17" s="198"/>
       <c r="C17" s="198"/>
@@ -15104,19 +15095,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="127" t="s">
-        <v>1222</v>
+        <v>1212</v>
       </c>
       <c r="B18" s="127" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="C18" s="127" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="D18" s="127" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="E18" s="127" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="F18" s="194"/>
       <c r="G18" s="195"/>
@@ -15124,7 +15115,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="127" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="B19" s="127">
         <f>B9*2*2.1*0.13</f>
@@ -15142,7 +15133,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="127" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B20" s="127">
         <f>B10*2*2.1*0.13</f>
@@ -15166,7 +15157,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="127" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B21" s="127">
         <f>B11*2*2.1*0.13</f>
@@ -15187,7 +15178,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="189" t="s">
-        <v>1223</v>
+        <v>1213</v>
       </c>
       <c r="B22" s="189">
         <f>SUM(B14:B21)</f>
@@ -15261,13 +15252,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
     </row>
     <row r="2" spans="1:5" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -15371,15 +15362,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -15540,15 +15531,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -15646,15 +15637,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -15741,7 +15732,7 @@
         <v>1109</v>
       </c>
       <c r="F6" s="239"/>
-      <c r="G6" s="213"/>
+      <c r="G6" s="207"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="139">
@@ -32826,15 +32817,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -32950,15 +32941,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -33038,15 +33029,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -33295,46 +33286,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="187" customWidth="1"/>
     <col min="2" max="2" width="9.88671875" style="112" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" style="112" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="112" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" style="112" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" style="112" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="112" customWidth="1"/>
     <col min="6" max="6" width="2" style="112" customWidth="1"/>
     <col min="7" max="7" width="8.21875" style="112" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="112" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="112" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" style="112" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="112"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-    </row>
-    <row r="2" spans="1:9" s="164" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+    </row>
+    <row r="2" spans="1:9" s="164" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="186" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
       <c r="H2" s="37" t="s">
         <v>10</v>
       </c>
@@ -33342,18 +33333,18 @@
         <v>830</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="164" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" s="164" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
+      <c r="B3" s="218" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="218"/>
+      <c r="G3" s="218"/>
       <c r="H3" s="115" t="s">
         <v>15</v>
       </c>
@@ -33362,18 +33353,18 @@
         <v>1688.585</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="164" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" s="164" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="207" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
+      <c r="B4" s="218" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
       <c r="H4" s="115" t="s">
         <v>15</v>
       </c>
@@ -33382,18 +33373,18 @@
         <v>1688.585</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="164" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="164" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="140">
         <v>3</v>
       </c>
-      <c r="B5" s="207" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C5" s="207"/>
-      <c r="D5" s="207"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="207"/>
-      <c r="G5" s="207"/>
+      <c r="B5" s="218" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C5" s="218"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="218"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="218"/>
       <c r="H5" s="115" t="s">
         <v>15</v>
       </c>
@@ -33406,14 +33397,14 @@
       <c r="A6" s="140">
         <v>4</v>
       </c>
-      <c r="B6" s="207" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C6" s="207"/>
-      <c r="D6" s="207"/>
-      <c r="E6" s="207"/>
-      <c r="F6" s="207"/>
-      <c r="G6" s="207"/>
+      <c r="B6" s="218" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C6" s="218"/>
+      <c r="D6" s="218"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
       <c r="H6" s="115" t="s">
         <v>15</v>
       </c>
@@ -33426,14 +33417,14 @@
       <c r="A7" s="140">
         <v>5</v>
       </c>
-      <c r="B7" s="207" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C7" s="207"/>
-      <c r="D7" s="207"/>
-      <c r="E7" s="207"/>
-      <c r="F7" s="207"/>
-      <c r="G7" s="207"/>
+      <c r="B7" s="218" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C7" s="218"/>
+      <c r="D7" s="218"/>
+      <c r="E7" s="218"/>
+      <c r="F7" s="218"/>
+      <c r="G7" s="218"/>
       <c r="H7" s="115" t="s">
         <v>15</v>
       </c>
@@ -33446,14 +33437,14 @@
       <c r="A8" s="140">
         <v>6</v>
       </c>
-      <c r="B8" s="207" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
+      <c r="B8" s="218" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="218"/>
       <c r="H8" s="115" t="s">
         <v>15</v>
       </c>
@@ -33466,14 +33457,14 @@
       <c r="A9" s="140">
         <v>7</v>
       </c>
-      <c r="B9" s="207" t="s">
-        <v>1205</v>
-      </c>
-      <c r="C9" s="207"/>
-      <c r="D9" s="207"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="207"/>
-      <c r="G9" s="207"/>
+      <c r="B9" s="218" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C9" s="218"/>
+      <c r="D9" s="218"/>
+      <c r="E9" s="218"/>
+      <c r="F9" s="218"/>
+      <c r="G9" s="218"/>
       <c r="H9" s="115" t="s">
         <v>15</v>
       </c>
@@ -33483,15 +33474,15 @@
       </c>
     </row>
     <row r="10" spans="1:9" s="164" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="208"/>
-      <c r="B10" s="209"/>
-      <c r="C10" s="210"/>
-      <c r="D10" s="216"/>
-      <c r="E10" s="217"/>
-      <c r="F10" s="217"/>
-      <c r="G10" s="217"/>
-      <c r="H10" s="217"/>
-      <c r="I10" s="217"/>
+      <c r="A10" s="215"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="217"/>
+      <c r="D10" s="210"/>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
+      <c r="G10" s="211"/>
+      <c r="H10" s="211"/>
+      <c r="I10" s="211"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="176" t="s">
@@ -33503,12 +33494,12 @@
       <c r="C11" s="176" t="s">
         <v>1191</v>
       </c>
-      <c r="D11" s="218"/>
-      <c r="E11" s="219"/>
-      <c r="F11" s="219"/>
-      <c r="G11" s="219"/>
-      <c r="H11" s="219"/>
-      <c r="I11" s="219"/>
+      <c r="D11" s="212"/>
+      <c r="E11" s="213"/>
+      <c r="F11" s="213"/>
+      <c r="G11" s="213"/>
+      <c r="H11" s="213"/>
+      <c r="I11" s="213"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="176">
@@ -33521,12 +33512,12 @@
         <f>C18+I18+C25+C32</f>
         <v>631.9</v>
       </c>
-      <c r="D12" s="218"/>
-      <c r="E12" s="219"/>
-      <c r="F12" s="219"/>
-      <c r="G12" s="219"/>
-      <c r="H12" s="219"/>
-      <c r="I12" s="219"/>
+      <c r="D12" s="212"/>
+      <c r="E12" s="213"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="213"/>
+      <c r="H12" s="213"/>
+      <c r="I12" s="213"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="176">
@@ -33539,12 +33530,12 @@
         <f>C19+I19+C26+C33</f>
         <v>559.50399999999991</v>
       </c>
-      <c r="D13" s="218"/>
-      <c r="E13" s="219"/>
-      <c r="F13" s="219"/>
-      <c r="G13" s="219"/>
-      <c r="H13" s="219"/>
-      <c r="I13" s="219"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="213"/>
+      <c r="F13" s="213"/>
+      <c r="G13" s="213"/>
+      <c r="H13" s="213"/>
+      <c r="I13" s="213"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="176">
@@ -33557,43 +33548,43 @@
         <f>C20+I20+C27+C34</f>
         <v>497.18099999999998</v>
       </c>
-      <c r="D14" s="218"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="219"/>
-      <c r="G14" s="219"/>
-      <c r="H14" s="219"/>
-      <c r="I14" s="219"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="213"/>
+      <c r="G14" s="213"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="213"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="214" t="s">
+      <c r="A15" s="208" t="s">
         <v>843</v>
       </c>
-      <c r="B15" s="214"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="176">
         <f>SUM(C12:C14)</f>
         <v>1688.585</v>
       </c>
-      <c r="D15" s="218"/>
-      <c r="E15" s="219"/>
-      <c r="F15" s="219"/>
-      <c r="G15" s="219"/>
-      <c r="H15" s="219"/>
-      <c r="I15" s="219"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="213"/>
+      <c r="F15" s="213"/>
+      <c r="G15" s="213"/>
+      <c r="H15" s="213"/>
+      <c r="I15" s="213"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="215" t="s">
+      <c r="A16" s="209" t="s">
         <v>1042</v>
       </c>
-      <c r="B16" s="215"/>
-      <c r="C16" s="215"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
       <c r="D16" s="195"/>
       <c r="E16" s="195"/>
       <c r="F16" s="195"/>
-      <c r="G16" s="220" t="s">
-        <v>1201</v>
-      </c>
-      <c r="H16" s="220"/>
-      <c r="I16" s="220"/>
+      <c r="G16" s="214" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H16" s="214"/>
+      <c r="I16" s="214"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="176" t="s">
@@ -33694,10 +33685,10 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="214" t="s">
+      <c r="A21" s="208" t="s">
         <v>843</v>
       </c>
-      <c r="B21" s="214"/>
+      <c r="B21" s="208"/>
       <c r="C21" s="176">
         <f>SUM(C18:C20)</f>
         <v>203.45099999999996</v>
@@ -33705,32 +33696,32 @@
       <c r="D21" s="195"/>
       <c r="E21" s="195"/>
       <c r="F21" s="195"/>
-      <c r="G21" s="214" t="s">
+      <c r="G21" s="208" t="s">
         <v>843</v>
       </c>
-      <c r="H21" s="214"/>
+      <c r="H21" s="208"/>
       <c r="I21" s="176">
         <f>SUM(I18:I20)</f>
         <v>37.827999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="208"/>
-      <c r="B22" s="209"/>
-      <c r="C22" s="210"/>
+      <c r="A22" s="215"/>
+      <c r="B22" s="216"/>
+      <c r="C22" s="217"/>
       <c r="D22" s="195"/>
       <c r="E22" s="195"/>
       <c r="F22" s="195"/>
-      <c r="G22" s="213"/>
-      <c r="H22" s="213"/>
-      <c r="I22" s="213"/>
+      <c r="G22" s="207"/>
+      <c r="H22" s="207"/>
+      <c r="I22" s="207"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="215" t="s">
+      <c r="A23" s="209" t="s">
         <v>878</v>
       </c>
-      <c r="B23" s="215"/>
-      <c r="C23" s="215"/>
+      <c r="B23" s="209"/>
+      <c r="C23" s="209"/>
       <c r="D23" s="195"/>
       <c r="E23" s="195"/>
       <c r="F23" s="195"/>
@@ -33810,10 +33801,10 @@
       <c r="I27" s="195"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="214" t="s">
+      <c r="A28" s="208" t="s">
         <v>843</v>
       </c>
-      <c r="B28" s="214"/>
+      <c r="B28" s="208"/>
       <c r="C28" s="176">
         <f>SUM(C25:C27)</f>
         <v>72.608999999999995</v>
@@ -33826,9 +33817,9 @@
       <c r="I28" s="195"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="208"/>
-      <c r="B29" s="209"/>
-      <c r="C29" s="210"/>
+      <c r="A29" s="215"/>
+      <c r="B29" s="216"/>
+      <c r="C29" s="217"/>
       <c r="D29" s="195"/>
       <c r="E29" s="195"/>
       <c r="F29" s="195"/>
@@ -33837,11 +33828,11 @@
       <c r="I29" s="195"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="215" t="s">
+      <c r="A30" s="209" t="s">
         <v>941</v>
       </c>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
+      <c r="B30" s="209"/>
+      <c r="C30" s="209"/>
       <c r="D30" s="195"/>
       <c r="E30" s="195"/>
       <c r="F30" s="195"/>
@@ -33921,10 +33912,10 @@
       <c r="I34" s="195"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="214" t="s">
+      <c r="A35" s="208" t="s">
         <v>843</v>
       </c>
-      <c r="B35" s="214"/>
+      <c r="B35" s="208"/>
       <c r="C35" s="176">
         <f>SUM(C32:C34)</f>
         <v>1374.6969999999999</v>
@@ -33936,25 +33927,18 @@
       <c r="H35" s="195"/>
       <c r="I35" s="195"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="112" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C37" s="112" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D37" s="112" t="s">
-        <v>1216</v>
-      </c>
-      <c r="E37" s="112" t="s">
-        <v>1215</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
     <mergeCell ref="G22:I35"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A16:C16"/>
@@ -33969,16 +33953,6 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -34004,19 +33978,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
     </row>
     <row r="2" spans="1:11" s="119" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -34056,11 +34030,11 @@
       <c r="D3" s="234"/>
       <c r="E3" s="234"/>
       <c r="F3" s="206"/>
-      <c r="G3" s="259" t="s">
+      <c r="G3" s="254" t="s">
         <v>1071</v>
       </c>
-      <c r="H3" s="260"/>
-      <c r="I3" s="261"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="256"/>
       <c r="J3" s="115" t="s">
         <v>15</v>
       </c>
@@ -34081,11 +34055,11 @@
       <c r="D4" s="252"/>
       <c r="E4" s="252"/>
       <c r="F4" s="253"/>
-      <c r="G4" s="262" t="s">
+      <c r="G4" s="257" t="s">
         <v>1073</v>
       </c>
-      <c r="H4" s="263"/>
-      <c r="I4" s="264"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="259"/>
       <c r="J4" s="128" t="s">
         <v>15</v>
       </c>
@@ -34106,11 +34080,11 @@
       <c r="D5" s="234"/>
       <c r="E5" s="234"/>
       <c r="F5" s="206"/>
-      <c r="G5" s="259" t="s">
+      <c r="G5" s="254" t="s">
         <v>1071</v>
       </c>
-      <c r="H5" s="260"/>
-      <c r="I5" s="261"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="256"/>
       <c r="J5" s="115" t="s">
         <v>15</v>
       </c>
@@ -34131,11 +34105,11 @@
       <c r="D6" s="252"/>
       <c r="E6" s="252"/>
       <c r="F6" s="253"/>
-      <c r="G6" s="262" t="s">
+      <c r="G6" s="257" t="s">
         <v>1073</v>
       </c>
-      <c r="H6" s="263"/>
-      <c r="I6" s="264"/>
+      <c r="H6" s="258"/>
+      <c r="I6" s="259"/>
       <c r="J6" s="128" t="s">
         <v>15</v>
       </c>
@@ -34156,11 +34130,11 @@
       <c r="D7" s="234"/>
       <c r="E7" s="234"/>
       <c r="F7" s="206"/>
-      <c r="G7" s="259" t="s">
+      <c r="G7" s="254" t="s">
         <v>1071</v>
       </c>
-      <c r="H7" s="260"/>
-      <c r="I7" s="261"/>
+      <c r="H7" s="255"/>
+      <c r="I7" s="256"/>
       <c r="J7" s="115" t="s">
         <v>15</v>
       </c>
@@ -34181,11 +34155,11 @@
       <c r="D8" s="252"/>
       <c r="E8" s="252"/>
       <c r="F8" s="253"/>
-      <c r="G8" s="262" t="s">
+      <c r="G8" s="257" t="s">
         <v>1073</v>
       </c>
-      <c r="H8" s="263"/>
-      <c r="I8" s="264"/>
+      <c r="H8" s="258"/>
+      <c r="I8" s="259"/>
       <c r="J8" s="128" t="s">
         <v>15</v>
       </c>
@@ -34216,7 +34190,7 @@
       <c r="C10" s="130" t="s">
         <v>1074</v>
       </c>
-      <c r="D10" s="256"/>
+      <c r="D10" s="262"/>
       <c r="E10" s="123" t="s">
         <v>829</v>
       </c>
@@ -34241,7 +34215,7 @@
       <c r="C11" s="125">
         <v>3.24</v>
       </c>
-      <c r="D11" s="256"/>
+      <c r="D11" s="262"/>
       <c r="E11" s="121">
         <v>28</v>
       </c>
@@ -34266,7 +34240,7 @@
       <c r="C12" s="125">
         <v>34.08</v>
       </c>
-      <c r="D12" s="256"/>
+      <c r="D12" s="262"/>
       <c r="E12" s="121">
         <v>29</v>
       </c>
@@ -34291,7 +34265,7 @@
       <c r="C13" s="125">
         <v>7.68</v>
       </c>
-      <c r="D13" s="256"/>
+      <c r="D13" s="262"/>
       <c r="E13" s="121">
         <v>30</v>
       </c>
@@ -34316,7 +34290,7 @@
       <c r="C14" s="125">
         <v>17.16</v>
       </c>
-      <c r="D14" s="256"/>
+      <c r="D14" s="262"/>
       <c r="E14" s="121">
         <v>31</v>
       </c>
@@ -34341,7 +34315,7 @@
       <c r="C15" s="125">
         <v>32.4</v>
       </c>
-      <c r="D15" s="256"/>
+      <c r="D15" s="262"/>
       <c r="E15" s="121">
         <v>32</v>
       </c>
@@ -34366,7 +34340,7 @@
       <c r="C16" s="125">
         <v>19.2</v>
       </c>
-      <c r="D16" s="256"/>
+      <c r="D16" s="262"/>
       <c r="E16" s="121">
         <v>33</v>
       </c>
@@ -34391,7 +34365,7 @@
       <c r="C17" s="125">
         <v>32.4</v>
       </c>
-      <c r="D17" s="256"/>
+      <c r="D17" s="262"/>
       <c r="E17" s="121">
         <v>34</v>
       </c>
@@ -34416,7 +34390,7 @@
       <c r="C18" s="125">
         <v>49.199999999999996</v>
       </c>
-      <c r="D18" s="256"/>
+      <c r="D18" s="262"/>
       <c r="E18" s="121">
         <v>35</v>
       </c>
@@ -34441,7 +34415,7 @@
       <c r="C19" s="125">
         <v>15.6</v>
       </c>
-      <c r="D19" s="256"/>
+      <c r="D19" s="262"/>
       <c r="E19" s="121">
         <v>36</v>
       </c>
@@ -34466,7 +34440,7 @@
       <c r="C20" s="125">
         <v>21.599999999999998</v>
       </c>
-      <c r="D20" s="256"/>
+      <c r="D20" s="262"/>
       <c r="E20" s="121">
         <v>37</v>
       </c>
@@ -34491,7 +34465,7 @@
       <c r="C21" s="125">
         <v>8.4</v>
       </c>
-      <c r="D21" s="256"/>
+      <c r="D21" s="262"/>
       <c r="E21" s="121">
         <v>38</v>
       </c>
@@ -34516,7 +34490,7 @@
       <c r="C22" s="125">
         <v>4.8</v>
       </c>
-      <c r="D22" s="256"/>
+      <c r="D22" s="262"/>
       <c r="E22" s="121">
         <v>39</v>
       </c>
@@ -34541,7 +34515,7 @@
       <c r="C23" s="125">
         <v>20.04</v>
       </c>
-      <c r="D23" s="256"/>
+      <c r="D23" s="262"/>
       <c r="E23" s="121">
         <v>40</v>
       </c>
@@ -34566,7 +34540,7 @@
       <c r="C24" s="125">
         <v>19.2</v>
       </c>
-      <c r="D24" s="256"/>
+      <c r="D24" s="262"/>
       <c r="E24" s="121">
         <v>41</v>
       </c>
@@ -34591,7 +34565,7 @@
       <c r="C25" s="125">
         <v>42</v>
       </c>
-      <c r="D25" s="256"/>
+      <c r="D25" s="262"/>
       <c r="E25" s="121">
         <v>42</v>
       </c>
@@ -34616,7 +34590,7 @@
       <c r="C26" s="125">
         <v>27.599999999999998</v>
       </c>
-      <c r="D26" s="256"/>
+      <c r="D26" s="262"/>
       <c r="E26" s="121">
         <v>43</v>
       </c>
@@ -34641,7 +34615,7 @@
       <c r="C27" s="125">
         <v>26.4</v>
       </c>
-      <c r="D27" s="256"/>
+      <c r="D27" s="262"/>
       <c r="E27" s="121">
         <v>44</v>
       </c>
@@ -34666,7 +34640,7 @@
       <c r="C28" s="125">
         <v>16.8</v>
       </c>
-      <c r="D28" s="256"/>
+      <c r="D28" s="262"/>
       <c r="E28" s="121">
         <v>45</v>
       </c>
@@ -34691,7 +34665,7 @@
       <c r="C29" s="125">
         <v>8.4</v>
       </c>
-      <c r="D29" s="256"/>
+      <c r="D29" s="262"/>
       <c r="E29" s="121">
         <v>46</v>
       </c>
@@ -34716,7 +34690,7 @@
       <c r="C30" s="125">
         <v>108</v>
       </c>
-      <c r="D30" s="256"/>
+      <c r="D30" s="262"/>
       <c r="E30" s="121">
         <v>47</v>
       </c>
@@ -34741,7 +34715,7 @@
       <c r="C31" s="125">
         <v>12.360000000000001</v>
       </c>
-      <c r="D31" s="256"/>
+      <c r="D31" s="262"/>
       <c r="E31" s="121">
         <v>48</v>
       </c>
@@ -34766,7 +34740,7 @@
       <c r="C32" s="125">
         <v>7.68</v>
       </c>
-      <c r="D32" s="256"/>
+      <c r="D32" s="262"/>
       <c r="E32" s="121">
         <v>49</v>
       </c>
@@ -34791,7 +34765,7 @@
       <c r="C33" s="125">
         <v>36</v>
       </c>
-      <c r="D33" s="256"/>
+      <c r="D33" s="262"/>
       <c r="E33" s="121">
         <v>50</v>
       </c>
@@ -34813,7 +34787,7 @@
         <f>SUM(C11:C33)</f>
         <v>570.24</v>
       </c>
-      <c r="D34" s="256"/>
+      <c r="D34" s="262"/>
       <c r="E34" s="121">
         <v>51</v>
       </c>
@@ -34829,10 +34803,10 @@
       <c r="K34" s="222"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="257"/>
-      <c r="B35" s="257"/>
-      <c r="C35" s="257"/>
-      <c r="D35" s="256"/>
+      <c r="A35" s="263"/>
+      <c r="B35" s="263"/>
+      <c r="C35" s="263"/>
+      <c r="D35" s="262"/>
       <c r="E35" s="121">
         <v>52</v>
       </c>
@@ -34848,10 +34822,10 @@
       <c r="K35" s="222"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="257"/>
-      <c r="B36" s="257"/>
-      <c r="C36" s="257"/>
-      <c r="D36" s="256"/>
+      <c r="A36" s="263"/>
+      <c r="B36" s="263"/>
+      <c r="C36" s="263"/>
+      <c r="D36" s="262"/>
       <c r="E36" s="121">
         <v>54</v>
       </c>
@@ -34867,10 +34841,10 @@
       <c r="K36" s="222"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="257"/>
-      <c r="B37" s="257"/>
-      <c r="C37" s="257"/>
-      <c r="D37" s="256"/>
+      <c r="A37" s="263"/>
+      <c r="B37" s="263"/>
+      <c r="C37" s="263"/>
+      <c r="D37" s="262"/>
       <c r="E37" s="121">
         <v>55</v>
       </c>
@@ -34886,12 +34860,12 @@
       <c r="K37" s="222"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="254"/>
-      <c r="B38" s="254"/>
-      <c r="C38" s="254"/>
-      <c r="D38" s="254"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="255"/>
+      <c r="A38" s="260"/>
+      <c r="B38" s="260"/>
+      <c r="C38" s="260"/>
+      <c r="D38" s="260"/>
+      <c r="E38" s="260"/>
+      <c r="F38" s="261"/>
       <c r="G38" s="125">
         <f>SUM(G11:G37)</f>
         <v>491.46</v>
@@ -34902,11 +34876,11 @@
       <c r="K38" s="222"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="258" t="s">
+      <c r="A39" s="264" t="s">
         <v>1080</v>
       </c>
-      <c r="B39" s="258"/>
-      <c r="C39" s="258"/>
+      <c r="B39" s="264"/>
+      <c r="C39" s="264"/>
       <c r="D39" s="139">
         <f>C34+G38</f>
         <v>1061.7</v>
@@ -34921,6 +34895,18 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="H10:K39"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="D10:D37"/>
+    <mergeCell ref="A35:C37"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -34931,18 +34917,6 @@
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="H10:K39"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="D10:D37"/>
-    <mergeCell ref="A35:C37"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -34968,17 +34942,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -35593,18 +35567,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="277" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
     </row>
     <row r="2" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
@@ -35772,12 +35746,12 @@
       <c r="A9" s="79">
         <v>7</v>
       </c>
-      <c r="B9" s="277" t="s">
+      <c r="B9" s="278" t="s">
         <v>1060</v>
       </c>
-      <c r="C9" s="278"/>
-      <c r="D9" s="278"/>
-      <c r="E9" s="279"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="280"/>
       <c r="F9" s="79" t="s">
         <v>1058</v>
       </c>
@@ -35796,16 +35770,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="280"/>
-      <c r="B10" s="280"/>
-      <c r="C10" s="280"/>
-      <c r="D10" s="280"/>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="280"/>
-      <c r="I10" s="280"/>
-      <c r="J10" s="281"/>
+      <c r="A10" s="281"/>
+      <c r="B10" s="281"/>
+      <c r="C10" s="281"/>
+      <c r="D10" s="281"/>
+      <c r="E10" s="281"/>
+      <c r="F10" s="281"/>
+      <c r="G10" s="281"/>
+      <c r="H10" s="281"/>
+      <c r="I10" s="281"/>
+      <c r="J10" s="282"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -35820,7 +35794,7 @@
       <c r="D11" s="86" t="s">
         <v>830</v>
       </c>
-      <c r="E11" s="283"/>
+      <c r="E11" s="284"/>
       <c r="F11" s="79" t="s">
         <v>1054</v>
       </c>
@@ -35833,7 +35807,7 @@
       <c r="I11" s="79" t="s">
         <v>830</v>
       </c>
-      <c r="J11" s="282"/>
+      <c r="J11" s="283"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="92">
@@ -35848,7 +35822,7 @@
       <c r="D12" s="95">
         <v>11.7</v>
       </c>
-      <c r="E12" s="283"/>
+      <c r="E12" s="284"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -35861,7 +35835,7 @@
       <c r="I12" s="93">
         <v>33</v>
       </c>
-      <c r="J12" s="282"/>
+      <c r="J12" s="283"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="102">
@@ -35876,7 +35850,7 @@
       <c r="D13" s="101">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E13" s="283"/>
+      <c r="E13" s="284"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -35889,7 +35863,7 @@
       <c r="I13" s="93">
         <v>14.1</v>
       </c>
-      <c r="J13" s="282"/>
+      <c r="J13" s="283"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="92">
@@ -35904,7 +35878,7 @@
       <c r="D14" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E14" s="283"/>
+      <c r="E14" s="284"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -35917,7 +35891,7 @@
       <c r="I14" s="93">
         <v>8.1</v>
       </c>
-      <c r="J14" s="282"/>
+      <c r="J14" s="283"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="102">
@@ -35932,7 +35906,7 @@
       <c r="D15" s="101">
         <v>2.6</v>
       </c>
-      <c r="E15" s="283"/>
+      <c r="E15" s="284"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -35945,7 +35919,7 @@
       <c r="I15" s="93">
         <v>65.8</v>
       </c>
-      <c r="J15" s="282"/>
+      <c r="J15" s="283"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="92">
@@ -35960,7 +35934,7 @@
       <c r="D16" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E16" s="283"/>
+      <c r="E16" s="284"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -35973,7 +35947,7 @@
       <c r="I16" s="93">
         <v>2.6</v>
       </c>
-      <c r="J16" s="282"/>
+      <c r="J16" s="283"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="92">
@@ -35988,7 +35962,7 @@
       <c r="D17" s="95">
         <v>11.7</v>
       </c>
-      <c r="E17" s="283"/>
+      <c r="E17" s="284"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -36001,7 +35975,7 @@
       <c r="I17" s="93">
         <v>13.6</v>
       </c>
-      <c r="J17" s="282"/>
+      <c r="J17" s="283"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="102">
@@ -36016,7 +35990,7 @@
       <c r="D18" s="101">
         <v>31.6</v>
       </c>
-      <c r="E18" s="283"/>
+      <c r="E18" s="284"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -36029,7 +36003,7 @@
       <c r="I18" s="93">
         <v>5.8</v>
       </c>
-      <c r="J18" s="282"/>
+      <c r="J18" s="283"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="92">
@@ -36044,7 +36018,7 @@
       <c r="D19" s="95">
         <v>5.9</v>
       </c>
-      <c r="E19" s="283"/>
+      <c r="E19" s="284"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -36057,7 +36031,7 @@
       <c r="I19" s="93">
         <v>67.8</v>
       </c>
-      <c r="J19" s="282"/>
+      <c r="J19" s="283"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="92">
@@ -36072,7 +36046,7 @@
       <c r="D20" s="95">
         <v>36.9</v>
       </c>
-      <c r="E20" s="283"/>
+      <c r="E20" s="284"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -36085,7 +36059,7 @@
       <c r="I20" s="93">
         <v>1.8</v>
       </c>
-      <c r="J20" s="282"/>
+      <c r="J20" s="283"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="92">
@@ -36100,7 +36074,7 @@
       <c r="D21" s="95">
         <v>33.9</v>
       </c>
-      <c r="E21" s="283"/>
+      <c r="E21" s="284"/>
       <c r="F21" s="93">
         <v>3</v>
       </c>
@@ -36113,7 +36087,7 @@
       <c r="I21" s="93">
         <v>35.4</v>
       </c>
-      <c r="J21" s="282"/>
+      <c r="J21" s="283"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="92">
@@ -36128,7 +36102,7 @@
       <c r="D22" s="95">
         <v>11.9</v>
       </c>
-      <c r="E22" s="283"/>
+      <c r="E22" s="284"/>
       <c r="F22" s="93">
         <v>3</v>
       </c>
@@ -36141,7 +36115,7 @@
       <c r="I22" s="93">
         <v>5.9</v>
       </c>
-      <c r="J22" s="282"/>
+      <c r="J22" s="283"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="102">
@@ -36156,7 +36130,7 @@
       <c r="D23" s="101">
         <v>5.7</v>
       </c>
-      <c r="E23" s="283"/>
+      <c r="E23" s="284"/>
       <c r="F23" s="93">
         <v>3</v>
       </c>
@@ -36169,7 +36143,7 @@
       <c r="I23" s="93">
         <v>29.5</v>
       </c>
-      <c r="J23" s="282"/>
+      <c r="J23" s="283"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="92">
@@ -36184,7 +36158,7 @@
       <c r="D24" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E24" s="283"/>
+      <c r="E24" s="284"/>
       <c r="F24" s="93">
         <v>3</v>
       </c>
@@ -36197,7 +36171,7 @@
       <c r="I24" s="93">
         <v>36.9</v>
       </c>
-      <c r="J24" s="282"/>
+      <c r="J24" s="283"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="102">
@@ -36212,7 +36186,7 @@
       <c r="D25" s="101">
         <v>1.8</v>
       </c>
-      <c r="E25" s="283"/>
+      <c r="E25" s="284"/>
       <c r="F25" s="93">
         <v>3</v>
       </c>
@@ -36225,7 +36199,7 @@
       <c r="I25" s="93">
         <v>36.5</v>
       </c>
-      <c r="J25" s="282"/>
+      <c r="J25" s="283"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="92">
@@ -36240,7 +36214,7 @@
       <c r="D26" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E26" s="283"/>
+      <c r="E26" s="284"/>
       <c r="F26" s="96">
         <v>3</v>
       </c>
@@ -36253,7 +36227,7 @@
       <c r="I26" s="96">
         <v>29.5</v>
       </c>
-      <c r="J26" s="282"/>
+      <c r="J26" s="283"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="102">
@@ -36268,7 +36242,7 @@
       <c r="D27" s="101">
         <v>44.2</v>
       </c>
-      <c r="E27" s="283"/>
+      <c r="E27" s="284"/>
       <c r="F27" s="98">
         <v>3</v>
       </c>
@@ -36282,22 +36256,22 @@
         <f>1.08*13.5</f>
         <v>14.580000000000002</v>
       </c>
-      <c r="J27" s="282"/>
+      <c r="J27" s="283"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="J10:J27"/>
+    <mergeCell ref="E11:E27"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="J10:J27"/>
-    <mergeCell ref="E11:E27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -36324,17 +36298,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="277" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
     </row>
     <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
@@ -36468,15 +36442,15 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="280"/>
-      <c r="B8" s="280"/>
-      <c r="C8" s="280"/>
-      <c r="D8" s="280"/>
-      <c r="E8" s="280"/>
-      <c r="F8" s="280"/>
-      <c r="G8" s="280"/>
-      <c r="H8" s="280"/>
-      <c r="I8" s="280"/>
+      <c r="A8" s="281"/>
+      <c r="B8" s="281"/>
+      <c r="C8" s="281"/>
+      <c r="D8" s="281"/>
+      <c r="E8" s="281"/>
+      <c r="F8" s="281"/>
+      <c r="G8" s="281"/>
+      <c r="H8" s="281"/>
+      <c r="I8" s="281"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -36491,7 +36465,7 @@
       <c r="D9" s="86" t="s">
         <v>830</v>
       </c>
-      <c r="E9" s="283"/>
+      <c r="E9" s="284"/>
       <c r="F9" s="79" t="s">
         <v>1054</v>
       </c>
@@ -36518,7 +36492,7 @@
       <c r="D10" s="82">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E10" s="283"/>
+      <c r="E10" s="284"/>
       <c r="F10" s="93">
         <v>3</v>
       </c>
@@ -36545,7 +36519,7 @@
       <c r="D11" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E11" s="283"/>
+      <c r="E11" s="284"/>
       <c r="F11" s="93">
         <v>3</v>
       </c>
@@ -36572,7 +36546,7 @@
       <c r="D12" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E12" s="283"/>
+      <c r="E12" s="284"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -36599,7 +36573,7 @@
       <c r="D13" s="82">
         <v>31.6</v>
       </c>
-      <c r="E13" s="283"/>
+      <c r="E13" s="284"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -36626,7 +36600,7 @@
       <c r="D14" s="95">
         <v>5.9</v>
       </c>
-      <c r="E14" s="283"/>
+      <c r="E14" s="284"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -36653,7 +36627,7 @@
       <c r="D15" s="95">
         <v>36.9</v>
       </c>
-      <c r="E15" s="283"/>
+      <c r="E15" s="284"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -36680,7 +36654,7 @@
       <c r="D16" s="95">
         <v>33.9</v>
       </c>
-      <c r="E16" s="283"/>
+      <c r="E16" s="284"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -36707,7 +36681,7 @@
       <c r="D17" s="82">
         <v>5.7</v>
       </c>
-      <c r="E17" s="283"/>
+      <c r="E17" s="284"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -36734,7 +36708,7 @@
       <c r="D18" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E18" s="283"/>
+      <c r="E18" s="284"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -36761,7 +36735,7 @@
       <c r="D19" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E19" s="283"/>
+      <c r="E19" s="284"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -36788,7 +36762,7 @@
       <c r="D20" s="82">
         <v>44.2</v>
       </c>
-      <c r="E20" s="283"/>
+      <c r="E20" s="284"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -36890,17 +36864,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -38138,16 +38112,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
       <c r="I1" s="224"/>
       <c r="J1" s="224"/>
       <c r="K1" s="224"/>
@@ -38162,13 +38136,13 @@
       <c r="A2" s="182" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
       <c r="G2" s="37" t="s">
         <v>10</v>
       </c>
@@ -38189,13 +38163,13 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="218" t="s">
         <v>1195</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="218"/>
       <c r="G3" s="115" t="s">
         <v>1196</v>
       </c>
@@ -39847,10 +39821,10 @@
       <c r="F8" s="226"/>
     </row>
     <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="214" t="s">
+      <c r="A9" s="208" t="s">
         <v>843</v>
       </c>
-      <c r="B9" s="214"/>
+      <c r="B9" s="208"/>
       <c r="C9" s="176">
         <f>SUM(C6:C8)</f>
         <v>2292</v>
@@ -39892,34 +39866,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
     </row>
     <row r="2" spans="1:11" s="164" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="170" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -39931,16 +39905,16 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="218" t="s">
         <v>1179</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="218"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="218"/>
+      <c r="I3" s="218"/>
       <c r="J3" s="115" t="s">
         <v>20</v>
       </c>
@@ -39985,19 +39959,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
       <c r="L1" s="195"/>
       <c r="M1" s="195"/>
       <c r="N1" s="195"/>
@@ -40009,16 +39983,16 @@
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="I2" s="212"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -40036,16 +40010,16 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="218" t="s">
         <v>1134</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="218"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="218"/>
+      <c r="I3" s="218"/>
       <c r="J3" s="115" t="s">
         <v>19</v>
       </c>
@@ -40064,16 +40038,16 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="207" t="s">
+      <c r="B4" s="218" t="s">
         <v>1135</v>
       </c>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="207"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
       <c r="J4" s="115" t="s">
         <v>19</v>
       </c>
@@ -41358,8 +41332,8 @@
         <v>18.628319999999995</v>
       </c>
       <c r="O36" s="222"/>
-      <c r="P36" s="213"/>
-      <c r="Q36" s="213"/>
+      <c r="P36" s="207"/>
+      <c r="Q36" s="207"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="166" t="s">
@@ -41381,8 +41355,8 @@
         <v>14.089440000000002</v>
       </c>
       <c r="I37" s="194"/>
-      <c r="J37" s="213"/>
-      <c r="K37" s="213"/>
+      <c r="J37" s="207"/>
+      <c r="K37" s="207"/>
       <c r="L37" s="221"/>
       <c r="M37" s="222"/>
       <c r="N37" s="222"/>
@@ -41431,16 +41405,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -41467,7 +41441,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="205" t="s">
-        <v>1225</v>
+        <v>1215</v>
       </c>
       <c r="C3" s="234"/>
       <c r="D3" s="234"/>
@@ -41530,7 +41504,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="205" t="s">
-        <v>1227</v>
+        <v>1217</v>
       </c>
       <c r="C6" s="234"/>
       <c r="D6" s="234"/>
@@ -41690,16 +41664,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -41774,7 +41748,7 @@
       <c r="D5" s="234"/>
       <c r="E5" s="206"/>
       <c r="F5" s="192" t="s">
-        <v>1226</v>
+        <v>1216</v>
       </c>
       <c r="G5" s="115" t="s">
         <v>15</v>
@@ -41918,15 +41892,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="219" t="s">
         <v>1194</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -41995,13 +41969,13 @@
       <c r="G5" s="201"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="220" t="s">
         <v>1180</v>
       </c>
-      <c r="B6" s="212"/>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
+      <c r="B6" s="220"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="220"/>
       <c r="F6" s="195"/>
       <c r="G6" s="195"/>
     </row>
